--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G8">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G13">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G21">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G38">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G42">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G47">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G60">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G82">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G86">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G80">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G86">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19588,10 +19588,10 @@
         <v>0</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE118">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G42">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G60">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G66">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G80">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G84">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G86">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G96">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G102">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G80">

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G70">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC116">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G54">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G56">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G64">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15338,10 +15338,10 @@
         <v>0</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15664,10 +15664,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15990,10 +15990,10 @@
         <v>0</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA96">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16805,10 +16805,10 @@
         <v>0</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16968,10 +16968,10 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17620,10 +17620,10 @@
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17783,10 +17783,10 @@
         <v>0</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA107">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G112">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18761,10 +18761,10 @@
         <v>0</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q117">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G18">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>4.82</v>
+        <v>4.14</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G47">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G56">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G70">

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC104">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -644,55 +644,55 @@
         <v>2.35</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>2.59</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA20">
         <v>1.95</v>
@@ -3614,19 +3614,19 @@
         <v>1.85</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>2.45</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>3.16</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA27">
         <v>1.87</v>
@@ -4755,19 +4755,19 @@
         <v>1.93</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,34 +5045,34 @@
         <v>6.97</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
         <v>1.85</v>
@@ -5081,19 +5081,19 @@
         <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,34 +5208,34 @@
         <v>2.55</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA30">
         <v>1.98</v>
@@ -5244,19 +5244,19 @@
         <v>1.83</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>5.54</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8305,34 +8305,34 @@
         <v>3.6</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA49">
         <v>1.9</v>
@@ -8341,19 +8341,19 @@
         <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P59">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O60">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G64">
@@ -10913,55 +10913,55 @@
         <v>2.03</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>2.39</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>4.32</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,34 +11402,34 @@
         <v>2.76</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA68">
         <v>1.93</v>
@@ -11438,19 +11438,19 @@
         <v>1.83</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,34 +13521,34 @@
         <v>4.75</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA81">
         <v>1.94</v>
@@ -13557,19 +13557,19 @@
         <v>1.86</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>3.91</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -17270,34 +17270,34 @@
         <v>4.55</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA104">
         <v>2.1</v>
@@ -17306,19 +17306,19 @@
         <v>1.65</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL104">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC7">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG7">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="R8">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="U8">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="V8">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG8">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>3.01</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P12">
-        <v>3.67</v>
+        <v>3.98</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="O17">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.02</v>
+        <v>3.51</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-27 07:00:00</t>
+          <t>2026-09-27 07:15:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-27 07:15:00</t>
+          <t>2026-09-27 07:30:00</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="O20">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="V20">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
+        <v>1.31</v>
+      </c>
+      <c r="Z20">
+        <v>2.92</v>
+      </c>
+      <c r="AA20">
+        <v>2.08</v>
+      </c>
+      <c r="AB20">
+        <v>1.64</v>
+      </c>
+      <c r="AC20">
+        <v>3.8</v>
+      </c>
+      <c r="AD20">
+        <v>1.19</v>
+      </c>
+      <c r="AE20">
+        <v>1.02</v>
+      </c>
+      <c r="AF20">
+        <v>1.81</v>
+      </c>
+      <c r="AG20">
+        <v>1.86</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.26</v>
       </c>
-      <c r="Z20">
-        <v>3.2</v>
-      </c>
-      <c r="AA20">
-        <v>1.95</v>
-      </c>
-      <c r="AB20">
-        <v>1.85</v>
-      </c>
-      <c r="AC20">
-        <v>3.14</v>
-      </c>
-      <c r="AD20">
-        <v>1.27</v>
-      </c>
-      <c r="AE20">
-        <v>1.07</v>
-      </c>
-      <c r="AF20">
-        <v>1.69</v>
-      </c>
-      <c r="AG20">
-        <v>2</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.24</v>
-      </c>
       <c r="AK20">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-27 07:30:00</t>
+          <t>2026-09-27 08:00:00</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4179,22 +4179,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="P24">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,17 +4380,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-27 08:00:00</t>
+          <t>2026-09-27 09:00:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="R27">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="V27">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z27">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB27">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AK27">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="Q28">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="R28">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="V28">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>4.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>2.41</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>2.42</v>
+        <v>3.12</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-27 09:00:00</t>
+          <t>2026-09-27 09:30:00</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.38</v>
+        <v>2.39</v>
       </c>
       <c r="O29">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>6.97</v>
+        <v>2.55</v>
       </c>
       <c r="Q29">
-        <v>1.75</v>
+        <v>3.04</v>
       </c>
       <c r="R29">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="S29">
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U29">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD29">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>2.27</v>
+        <v>1.69</v>
       </c>
       <c r="AG29">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>3.12</v>
+        <v>1.43</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="O33">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q33">
+        <v>1.72</v>
+      </c>
+      <c r="R33">
         <v>2.31</v>
       </c>
-      <c r="R33">
-        <v>2.85</v>
-      </c>
       <c r="S33">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>4.8</v>
+        <v>2.72</v>
       </c>
       <c r="U33">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="V33">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
+        <v>1.27</v>
+      </c>
+      <c r="Z33">
+        <v>3.14</v>
+      </c>
+      <c r="AA33">
+        <v>2</v>
+      </c>
+      <c r="AB33">
+        <v>1.8</v>
+      </c>
+      <c r="AC33">
+        <v>3.28</v>
+      </c>
+      <c r="AD33">
+        <v>1.25</v>
+      </c>
+      <c r="AE33">
+        <v>1.05</v>
+      </c>
+      <c r="AF33">
+        <v>2.63</v>
+      </c>
+      <c r="AG33">
+        <v>1.41</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.03</v>
       </c>
-      <c r="Z33">
-        <v>7.3</v>
-      </c>
-      <c r="AA33">
-        <v>1.28</v>
-      </c>
-      <c r="AB33">
-        <v>3.6</v>
-      </c>
-      <c r="AC33">
-        <v>1.66</v>
-      </c>
-      <c r="AD33">
-        <v>2.12</v>
-      </c>
-      <c r="AE33">
-        <v>1.51</v>
-      </c>
-      <c r="AF33">
-        <v>1.27</v>
-      </c>
-      <c r="AG33">
-        <v>3.34</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.28</v>
-      </c>
       <c r="AK33">
-        <v>1.84</v>
+        <v>3.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-27 09:30:00</t>
+          <t>2026-09-27 10:00:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>4.14</v>
+        <v>4.34</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q37">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U37">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.15</v>
+      </c>
+      <c r="Z37">
+        <v>4.6</v>
+      </c>
+      <c r="AA37">
+        <v>1.55</v>
+      </c>
+      <c r="AB37">
+        <v>2.42</v>
+      </c>
+      <c r="AC37">
+        <v>2.33</v>
+      </c>
+      <c r="AD37">
+        <v>1.53</v>
+      </c>
+      <c r="AE37">
         <v>1.18</v>
       </c>
-      <c r="Z37">
-        <v>4.1</v>
-      </c>
-      <c r="AA37">
-        <v>1.68</v>
-      </c>
-      <c r="AB37">
-        <v>2.07</v>
-      </c>
-      <c r="AC37">
-        <v>2.6</v>
-      </c>
-      <c r="AD37">
-        <v>1.43</v>
-      </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-27 10:00:00</t>
+          <t>2026-09-27 10:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-27 10:30:00</t>
+          <t>2026-09-27 11:00:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G47">
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-27 11:00:00</t>
+          <t>2026-09-27 11:15:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-27 11:15:00</t>
+          <t>2026-09-27 11:45:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-27 11:45:00</t>
+          <t>2026-09-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O59">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G63">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00:00</t>
+          <t>2026-09-27 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.29</v>
+        <v>2.6</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P65">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="Q65">
-        <v>4.18</v>
+        <v>3.58</v>
       </c>
       <c r="R65">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T65">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V65">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X65">
         <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z65">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA65">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB65">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC65">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE65">
         <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG65">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="P66">
-        <v>2.39</v>
+        <v>4.32</v>
       </c>
       <c r="Q66">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S66">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T66">
         <v>2.75</v>
       </c>
       <c r="U66">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="V66">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W66">
         <v>1.02</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z66">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA66">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AB66">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AC66">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AD66">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE66">
         <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AG66">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="O67">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P67">
-        <v>4.32</v>
+        <v>2.76</v>
       </c>
       <c r="Q67">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R67">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="S67">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="T67">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="U67">
-        <v>2.99</v>
+        <v>2.34</v>
       </c>
       <c r="V67">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AA67">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AB67">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC67">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD67">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="AG67">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK67">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="O68">
-        <v>3.38</v>
+        <v>2.99</v>
       </c>
       <c r="P68">
-        <v>2.76</v>
+        <v>3.01</v>
       </c>
       <c r="Q68">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="R68">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="S68">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T68">
-        <v>3.11</v>
+        <v>2.51</v>
       </c>
       <c r="U68">
-        <v>2.34</v>
+        <v>3.06</v>
       </c>
       <c r="V68">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="Z68">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="AA68">
+        <v>2.35</v>
+      </c>
+      <c r="AB68">
+        <v>1.55</v>
+      </c>
+      <c r="AC68">
+        <v>4.2</v>
+      </c>
+      <c r="AD68">
+        <v>1.16</v>
+      </c>
+      <c r="AE68">
+        <v>1.01</v>
+      </c>
+      <c r="AF68">
         <v>1.93</v>
       </c>
-      <c r="AB68">
-        <v>1.83</v>
-      </c>
-      <c r="AC68">
-        <v>2.66</v>
-      </c>
-      <c r="AD68">
-        <v>1.37</v>
-      </c>
-      <c r="AE68">
-        <v>1.1</v>
-      </c>
-      <c r="AF68">
-        <v>1.6</v>
-      </c>
       <c r="AG68">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X70">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK70">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-09-27 12:30:00</t>
+          <t>2026-09-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC88">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q36">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U36">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
         <v>1.13</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
+        <v>1.15</v>
+      </c>
+      <c r="Z36">
+        <v>4.6</v>
+      </c>
+      <c r="AA36">
+        <v>1.55</v>
+      </c>
+      <c r="AB36">
+        <v>2.42</v>
+      </c>
+      <c r="AC36">
+        <v>2.33</v>
+      </c>
+      <c r="AD36">
+        <v>1.53</v>
+      </c>
+      <c r="AE36">
         <v>1.18</v>
       </c>
-      <c r="Z36">
-        <v>4.1</v>
-      </c>
-      <c r="AA36">
-        <v>1.68</v>
-      </c>
-      <c r="AB36">
-        <v>2.07</v>
-      </c>
-      <c r="AC36">
-        <v>2.6</v>
-      </c>
-      <c r="AD36">
-        <v>1.43</v>
-      </c>
-      <c r="AE36">
-        <v>1.13</v>
-      </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
         <v>2.1</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD37">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q93">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>3.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>3.4</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,34 +9609,34 @@
         <v>2.7</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA57">
         <v>2.03</v>
@@ -9645,19 +9645,19 @@
         <v>1.78</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G58">
@@ -9766,61 +9766,61 @@
         <v>2.1</v>
       </c>
       <c r="O58">
+        <v>3.2</v>
+      </c>
+      <c r="P58">
         <v>3.1</v>
       </c>
-      <c r="P58">
-        <v>3.2</v>
-      </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G59">
@@ -9929,61 +9929,61 @@
         <v>2.1</v>
       </c>
       <c r="O59">
+        <v>3.1</v>
+      </c>
+      <c r="P59">
         <v>3.2</v>
       </c>
-      <c r="P59">
-        <v>3.1</v>
-      </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>2.25</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -16455,55 +16455,55 @@
         <v>3.49</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL99">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
         <v>1.13</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC36">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
         <v>2.1</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q37">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U37">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.15</v>
+      </c>
+      <c r="Z37">
+        <v>4.6</v>
+      </c>
+      <c r="AA37">
+        <v>1.55</v>
+      </c>
+      <c r="AB37">
+        <v>2.42</v>
+      </c>
+      <c r="AC37">
+        <v>2.33</v>
+      </c>
+      <c r="AD37">
+        <v>1.53</v>
+      </c>
+      <c r="AE37">
         <v>1.18</v>
       </c>
-      <c r="Z37">
-        <v>4.1</v>
-      </c>
-      <c r="AA37">
-        <v>1.68</v>
-      </c>
-      <c r="AB37">
-        <v>2.07</v>
-      </c>
-      <c r="AC37">
-        <v>2.6</v>
-      </c>
-      <c r="AD37">
-        <v>1.43</v>
-      </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -7979,55 +7979,55 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P56">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q56">
-        <v>2.62</v>
+        <v>3.26</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S56">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="U56">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="V56">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W56">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA56">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB56">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC56">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AD56">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE56">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG56">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
+        <v>3.2</v>
+      </c>
+      <c r="Q57">
+        <v>2.88</v>
+      </c>
+      <c r="R57">
+        <v>1.95</v>
+      </c>
+      <c r="S57">
+        <v>1.44</v>
+      </c>
+      <c r="T57">
+        <v>2.45</v>
+      </c>
+      <c r="U57">
+        <v>3.24</v>
+      </c>
+      <c r="V57">
+        <v>1.26</v>
+      </c>
+      <c r="W57">
+        <v>1.03</v>
+      </c>
+      <c r="X57">
+        <v>1.05</v>
+      </c>
+      <c r="Y57">
+        <v>1.36</v>
+      </c>
+      <c r="Z57">
         <v>2.7</v>
       </c>
-      <c r="Q57">
-        <v>3.26</v>
-      </c>
-      <c r="R57">
-        <v>2.06</v>
-      </c>
-      <c r="S57">
-        <v>1.35</v>
-      </c>
-      <c r="T57">
-        <v>2.77</v>
-      </c>
-      <c r="U57">
-        <v>2.65</v>
-      </c>
-      <c r="V57">
-        <v>1.38</v>
-      </c>
-      <c r="W57">
-        <v>1.06</v>
-      </c>
-      <c r="X57">
+      <c r="AA57">
+        <v>2.2</v>
+      </c>
+      <c r="AB57">
+        <v>1.57</v>
+      </c>
+      <c r="AC57">
+        <v>4.2</v>
+      </c>
+      <c r="AD57">
+        <v>1.15</v>
+      </c>
+      <c r="AE57">
         <v>1.02</v>
       </c>
-      <c r="Y57">
-        <v>1.28</v>
-      </c>
-      <c r="Z57">
-        <v>3.08</v>
-      </c>
-      <c r="AA57">
-        <v>2.03</v>
-      </c>
-      <c r="AB57">
-        <v>1.78</v>
-      </c>
-      <c r="AC57">
-        <v>3.28</v>
-      </c>
-      <c r="AD57">
-        <v>1.25</v>
-      </c>
-      <c r="AE57">
-        <v>1.06</v>
-      </c>
       <c r="AF57">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AG57">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK57">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O58">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q58">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R58">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="U58">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X58">
+        <v>1.04</v>
+      </c>
+      <c r="Y58">
+        <v>1.35</v>
+      </c>
+      <c r="Z58">
+        <v>2.74</v>
+      </c>
+      <c r="AA58">
+        <v>2.12</v>
+      </c>
+      <c r="AB58">
+        <v>1.62</v>
+      </c>
+      <c r="AC58">
+        <v>3.8</v>
+      </c>
+      <c r="AD58">
+        <v>1.19</v>
+      </c>
+      <c r="AE58">
         <v>1.03</v>
       </c>
-      <c r="Y58">
-        <v>1.32</v>
-      </c>
-      <c r="Z58">
-        <v>2.88</v>
-      </c>
-      <c r="AA58">
-        <v>2.04</v>
-      </c>
-      <c r="AB58">
-        <v>1.67</v>
-      </c>
-      <c r="AC58">
-        <v>3.5</v>
-      </c>
-      <c r="AD58">
-        <v>1.22</v>
-      </c>
-      <c r="AE58">
-        <v>1.05</v>
-      </c>
       <c r="AF58">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AG58">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G59">
@@ -9929,77 +9929,77 @@
         <v>2.1</v>
       </c>
       <c r="O59">
+        <v>3.2</v>
+      </c>
+      <c r="P59">
         <v>3.1</v>
       </c>
-      <c r="P59">
-        <v>3.2</v>
-      </c>
       <c r="Q59">
+        <v>2.8</v>
+      </c>
+      <c r="R59">
+        <v>2.02</v>
+      </c>
+      <c r="S59">
+        <v>1.37</v>
+      </c>
+      <c r="T59">
+        <v>2.69</v>
+      </c>
+      <c r="U59">
+        <v>2.81</v>
+      </c>
+      <c r="V59">
+        <v>1.34</v>
+      </c>
+      <c r="W59">
+        <v>1.05</v>
+      </c>
+      <c r="X59">
+        <v>1.03</v>
+      </c>
+      <c r="Y59">
+        <v>1.32</v>
+      </c>
+      <c r="Z59">
         <v>2.88</v>
       </c>
-      <c r="R59">
-        <v>1.95</v>
-      </c>
-      <c r="S59">
-        <v>1.44</v>
-      </c>
-      <c r="T59">
-        <v>2.45</v>
-      </c>
-      <c r="U59">
-        <v>3.24</v>
-      </c>
-      <c r="V59">
+      <c r="AA59">
+        <v>2.04</v>
+      </c>
+      <c r="AB59">
+        <v>1.67</v>
+      </c>
+      <c r="AC59">
+        <v>3.5</v>
+      </c>
+      <c r="AD59">
+        <v>1.22</v>
+      </c>
+      <c r="AE59">
+        <v>1.05</v>
+      </c>
+      <c r="AF59">
+        <v>1.82</v>
+      </c>
+      <c r="AG59">
+        <v>1.84</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
         <v>1.26</v>
       </c>
-      <c r="W59">
-        <v>1.03</v>
-      </c>
-      <c r="X59">
-        <v>1.05</v>
-      </c>
-      <c r="Y59">
-        <v>1.36</v>
-      </c>
-      <c r="Z59">
-        <v>2.7</v>
-      </c>
-      <c r="AA59">
-        <v>2.2</v>
-      </c>
-      <c r="AB59">
-        <v>1.57</v>
-      </c>
-      <c r="AC59">
-        <v>4.2</v>
-      </c>
-      <c r="AD59">
-        <v>1.15</v>
-      </c>
-      <c r="AE59">
-        <v>1.02</v>
-      </c>
-      <c r="AF59">
-        <v>1.92</v>
-      </c>
-      <c r="AG59">
-        <v>1.77</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>1.27</v>
-      </c>
       <c r="AK59">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="O81">
-        <v>3.74</v>
+        <v>3.43</v>
       </c>
       <c r="P81">
-        <v>4.75</v>
+        <v>3.91</v>
       </c>
       <c r="Q81">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R81">
         <v>2.1</v>
       </c>
       <c r="S81">
+        <v>1.36</v>
+      </c>
+      <c r="T81">
+        <v>2.95</v>
+      </c>
+      <c r="U81">
+        <v>2.8</v>
+      </c>
+      <c r="V81">
         <v>1.4</v>
       </c>
-      <c r="T81">
-        <v>2.75</v>
-      </c>
-      <c r="U81">
-        <v>2.78</v>
-      </c>
-      <c r="V81">
-        <v>1.33</v>
-      </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z81">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA81">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB81">
         <v>1.86</v>
       </c>
       <c r="AC81">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD81">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE81">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF81">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AG81">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK81">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="O82">
-        <v>3.43</v>
+        <v>3.74</v>
       </c>
       <c r="P82">
-        <v>3.91</v>
+        <v>4.75</v>
       </c>
       <c r="Q82">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R82">
         <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U82">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V82">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z82">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA82">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB82">
         <v>1.86</v>
       </c>
       <c r="AC82">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD82">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE82">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF82">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AG82">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -15151,34 +15151,34 @@
         <v>2.2</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA91">
         <v>1.9</v>
@@ -15187,19 +15187,19 @@
         <v>1.9</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O97">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="P97">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA97">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB97">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O98">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="P98">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>4.05</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19226,34 +19226,34 @@
         <v>5.57</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA116">
         <v>2.2</v>
@@ -19262,19 +19262,19 @@
         <v>1.6</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL116">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q36">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U36">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
         <v>1.13</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
+        <v>1.15</v>
+      </c>
+      <c r="Z36">
+        <v>4.6</v>
+      </c>
+      <c r="AA36">
+        <v>1.55</v>
+      </c>
+      <c r="AB36">
+        <v>2.42</v>
+      </c>
+      <c r="AC36">
+        <v>2.33</v>
+      </c>
+      <c r="AD36">
+        <v>1.53</v>
+      </c>
+      <c r="AE36">
         <v>1.18</v>
       </c>
-      <c r="Z36">
-        <v>4.1</v>
-      </c>
-      <c r="AA36">
-        <v>1.68</v>
-      </c>
-      <c r="AB36">
-        <v>2.07</v>
-      </c>
-      <c r="AC36">
-        <v>2.6</v>
-      </c>
-      <c r="AD36">
-        <v>1.43</v>
-      </c>
-      <c r="AE36">
-        <v>1.13</v>
-      </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
         <v>2.1</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD37">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O56">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
+        <v>3.2</v>
+      </c>
+      <c r="Q56">
+        <v>2.88</v>
+      </c>
+      <c r="R56">
+        <v>1.95</v>
+      </c>
+      <c r="S56">
+        <v>1.44</v>
+      </c>
+      <c r="T56">
+        <v>2.45</v>
+      </c>
+      <c r="U56">
+        <v>3.24</v>
+      </c>
+      <c r="V56">
+        <v>1.26</v>
+      </c>
+      <c r="W56">
+        <v>1.03</v>
+      </c>
+      <c r="X56">
+        <v>1.05</v>
+      </c>
+      <c r="Y56">
+        <v>1.36</v>
+      </c>
+      <c r="Z56">
         <v>2.7</v>
       </c>
-      <c r="Q56">
-        <v>3.26</v>
-      </c>
-      <c r="R56">
-        <v>2.06</v>
-      </c>
-      <c r="S56">
-        <v>1.35</v>
-      </c>
-      <c r="T56">
-        <v>2.77</v>
-      </c>
-      <c r="U56">
-        <v>2.65</v>
-      </c>
-      <c r="V56">
-        <v>1.38</v>
-      </c>
-      <c r="W56">
-        <v>1.06</v>
-      </c>
-      <c r="X56">
+      <c r="AA56">
+        <v>2.2</v>
+      </c>
+      <c r="AB56">
+        <v>1.57</v>
+      </c>
+      <c r="AC56">
+        <v>4.2</v>
+      </c>
+      <c r="AD56">
+        <v>1.15</v>
+      </c>
+      <c r="AE56">
         <v>1.02</v>
       </c>
-      <c r="Y56">
-        <v>1.28</v>
-      </c>
-      <c r="Z56">
-        <v>3.08</v>
-      </c>
-      <c r="AA56">
-        <v>2.03</v>
-      </c>
-      <c r="AB56">
-        <v>1.78</v>
-      </c>
-      <c r="AC56">
-        <v>3.28</v>
-      </c>
-      <c r="AD56">
-        <v>1.25</v>
-      </c>
-      <c r="AE56">
-        <v>1.06</v>
-      </c>
       <c r="AF56">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AG56">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK56">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O57">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R57">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="U57">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="V57">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W57">
+        <v>1.04</v>
+      </c>
+      <c r="X57">
+        <v>1.04</v>
+      </c>
+      <c r="Y57">
+        <v>1.35</v>
+      </c>
+      <c r="Z57">
+        <v>2.74</v>
+      </c>
+      <c r="AA57">
+        <v>2.12</v>
+      </c>
+      <c r="AB57">
+        <v>1.62</v>
+      </c>
+      <c r="AC57">
+        <v>3.8</v>
+      </c>
+      <c r="AD57">
+        <v>1.19</v>
+      </c>
+      <c r="AE57">
         <v>1.03</v>
       </c>
-      <c r="X57">
-        <v>1.05</v>
-      </c>
-      <c r="Y57">
-        <v>1.36</v>
-      </c>
-      <c r="Z57">
-        <v>2.7</v>
-      </c>
-      <c r="AA57">
-        <v>2.2</v>
-      </c>
-      <c r="AB57">
-        <v>1.57</v>
-      </c>
-      <c r="AC57">
-        <v>4.2</v>
-      </c>
-      <c r="AD57">
-        <v>1.15</v>
-      </c>
-      <c r="AE57">
-        <v>1.02</v>
-      </c>
       <c r="AF57">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG57">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q58">
-        <v>2.62</v>
+        <v>3.26</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T58">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="U58">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="V58">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W58">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB58">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC58">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AD58">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="O81">
-        <v>3.43</v>
+        <v>3.74</v>
       </c>
       <c r="P81">
-        <v>3.91</v>
+        <v>4.75</v>
       </c>
       <c r="Q81">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R81">
         <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U81">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA81">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB81">
         <v>1.86</v>
       </c>
       <c r="AC81">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD81">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE81">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF81">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AG81">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="O82">
-        <v>3.74</v>
+        <v>3.43</v>
       </c>
       <c r="P82">
-        <v>4.75</v>
+        <v>3.91</v>
       </c>
       <c r="Q82">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R82">
         <v>2.1</v>
       </c>
       <c r="S82">
+        <v>1.36</v>
+      </c>
+      <c r="T82">
+        <v>2.95</v>
+      </c>
+      <c r="U82">
+        <v>2.8</v>
+      </c>
+      <c r="V82">
         <v>1.4</v>
       </c>
-      <c r="T82">
-        <v>2.75</v>
-      </c>
-      <c r="U82">
-        <v>2.78</v>
-      </c>
-      <c r="V82">
-        <v>1.33</v>
-      </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA82">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB82">
         <v>1.86</v>
       </c>
       <c r="AC82">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD82">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF82">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AG82">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O97">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="P97">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="Q97">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S97">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T97">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U97">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V97">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W97">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y97">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z97">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA97">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AB97">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AC97">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD97">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG97">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK97">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O98">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="P98">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA98">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AB98">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>2.74</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19389,55 +19389,55 @@
         <v>2.66</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL117">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
         <v>1.13</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC36">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
         <v>2.1</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q37">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U37">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.15</v>
+      </c>
+      <c r="Z37">
+        <v>4.6</v>
+      </c>
+      <c r="AA37">
+        <v>1.55</v>
+      </c>
+      <c r="AB37">
+        <v>2.42</v>
+      </c>
+      <c r="AC37">
+        <v>2.33</v>
+      </c>
+      <c r="AD37">
+        <v>1.53</v>
+      </c>
+      <c r="AE37">
         <v>1.18</v>
       </c>
-      <c r="Z37">
-        <v>4.1</v>
-      </c>
-      <c r="AA37">
-        <v>1.68</v>
-      </c>
-      <c r="AB37">
-        <v>2.07</v>
-      </c>
-      <c r="AC37">
-        <v>2.6</v>
-      </c>
-      <c r="AD37">
-        <v>1.43</v>
-      </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P58">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U58">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="V58">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z58">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB58">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC58">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG58">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK58">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P59">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="R59">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S59">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U59">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V59">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W59">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA59">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB59">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC59">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.29</v>
+        <v>2.6</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P64">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="Q64">
-        <v>4.18</v>
+        <v>3.58</v>
       </c>
       <c r="R64">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T64">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V64">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X64">
         <v>1</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z64">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA64">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB64">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC64">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD64">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE64">
         <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG64">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="O65">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="Q65">
-        <v>3.58</v>
+        <v>4.18</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S65">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U65">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V65">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W65">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
         <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA65">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB65">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC65">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
         <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG65">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="O68">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="P68">
-        <v>3.01</v>
+        <v>2.49</v>
       </c>
       <c r="Q68">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="R68">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="S68">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T68">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="U68">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="V68">
+        <v>1.32</v>
+      </c>
+      <c r="W68">
+        <v>1.07</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
         <v>1.29</v>
       </c>
-      <c r="W68">
-        <v>1.05</v>
-      </c>
-      <c r="X68">
-        <v>1.03</v>
-      </c>
-      <c r="Y68">
-        <v>1.38</v>
-      </c>
       <c r="Z68">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AA68">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AB68">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AC68">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD68">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF68">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,65 +11556,65 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="O69">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="P69">
-        <v>2.49</v>
+        <v>3.01</v>
       </c>
       <c r="Q69">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="R69">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="S69">
+        <v>1.42</v>
+      </c>
+      <c r="T69">
+        <v>2.51</v>
+      </c>
+      <c r="U69">
+        <v>3.06</v>
+      </c>
+      <c r="V69">
+        <v>1.29</v>
+      </c>
+      <c r="W69">
+        <v>1.05</v>
+      </c>
+      <c r="X69">
+        <v>1.03</v>
+      </c>
+      <c r="Y69">
         <v>1.38</v>
       </c>
-      <c r="T69">
-        <v>2.64</v>
-      </c>
-      <c r="U69">
-        <v>2.89</v>
-      </c>
-      <c r="V69">
-        <v>1.32</v>
-      </c>
-      <c r="W69">
-        <v>1.07</v>
-      </c>
-      <c r="X69">
+      <c r="Z69">
+        <v>2.62</v>
+      </c>
+      <c r="AA69">
+        <v>2.35</v>
+      </c>
+      <c r="AB69">
+        <v>1.55</v>
+      </c>
+      <c r="AC69">
+        <v>4.2</v>
+      </c>
+      <c r="AD69">
+        <v>1.16</v>
+      </c>
+      <c r="AE69">
         <v>1.01</v>
       </c>
-      <c r="Y69">
-        <v>1.29</v>
-      </c>
-      <c r="Z69">
-        <v>3.04</v>
-      </c>
-      <c r="AA69">
-        <v>1.98</v>
-      </c>
-      <c r="AB69">
-        <v>1.71</v>
-      </c>
-      <c r="AC69">
-        <v>3.48</v>
-      </c>
-      <c r="AD69">
-        <v>1.22</v>
-      </c>
-      <c r="AE69">
-        <v>1.04</v>
-      </c>
       <c r="AF69">
+        <v>1.93</v>
+      </c>
+      <c r="AG69">
         <v>1.75</v>
       </c>
-      <c r="AG69">
-        <v>1.9</v>
-      </c>
       <c r="AH69" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.38</v>
+        <v>2.39</v>
       </c>
       <c r="O28">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="P28">
-        <v>6.97</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
-        <v>1.75</v>
+        <v>3.04</v>
       </c>
       <c r="R28">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="S28">
         <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U28">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>2.27</v>
+        <v>1.69</v>
       </c>
       <c r="AG28">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>3.12</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.39</v>
+        <v>1.38</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="P29">
-        <v>2.55</v>
+        <v>6.97</v>
       </c>
       <c r="Q29">
-        <v>3.04</v>
+        <v>1.75</v>
       </c>
       <c r="R29">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="S29">
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK29">
-        <v>1.43</v>
+        <v>3.12</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q57">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S57">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T57">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="U57">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V57">
+        <v>1.34</v>
+      </c>
+      <c r="W57">
+        <v>1.05</v>
+      </c>
+      <c r="X57">
+        <v>1.03</v>
+      </c>
+      <c r="Y57">
         <v>1.32</v>
       </c>
-      <c r="W57">
-        <v>1.04</v>
-      </c>
-      <c r="X57">
-        <v>1.04</v>
-      </c>
-      <c r="Y57">
-        <v>1.35</v>
-      </c>
       <c r="Z57">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA57">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AB57">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC57">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD57">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG57">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK57">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O58">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q58">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="R58">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S58">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T58">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U58">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB58">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC58">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O59">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P59">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q59">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="R59">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S59">
+        <v>1.4</v>
+      </c>
+      <c r="T59">
+        <v>2.58</v>
+      </c>
+      <c r="U59">
+        <v>2.9</v>
+      </c>
+      <c r="V59">
+        <v>1.32</v>
+      </c>
+      <c r="W59">
+        <v>1.04</v>
+      </c>
+      <c r="X59">
+        <v>1.04</v>
+      </c>
+      <c r="Y59">
         <v>1.35</v>
       </c>
-      <c r="T59">
-        <v>2.77</v>
-      </c>
-      <c r="U59">
-        <v>2.65</v>
-      </c>
-      <c r="V59">
-        <v>1.38</v>
-      </c>
-      <c r="W59">
-        <v>1.06</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.28</v>
-      </c>
       <c r="Z59">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA59">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB59">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC59">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD59">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF59">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AG59">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10291,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC61">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC63">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU118"/>
+  <dimension ref="A1:AU120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4067,55 +4067,55 @@
         <v>3.64</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.39</v>
+        <v>1.38</v>
       </c>
       <c r="O28">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
-        <v>2.55</v>
+        <v>6.97</v>
       </c>
       <c r="Q28">
-        <v>3.04</v>
+        <v>1.75</v>
       </c>
       <c r="R28">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="S28">
         <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>1.43</v>
+        <v>3.12</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.38</v>
+        <v>2.39</v>
       </c>
       <c r="O29">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>6.97</v>
+        <v>2.55</v>
       </c>
       <c r="Q29">
-        <v>1.75</v>
+        <v>3.04</v>
       </c>
       <c r="R29">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="S29">
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U29">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD29">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>2.27</v>
+        <v>1.69</v>
       </c>
       <c r="AG29">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>3.12</v>
+        <v>1.43</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7979,55 +7979,55 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
+        <v>1.41</v>
+      </c>
+      <c r="T47">
+        <v>2.62</v>
+      </c>
+      <c r="U47">
+        <v>2.72</v>
+      </c>
+      <c r="V47">
         <v>1.39</v>
       </c>
-      <c r="T47">
-        <v>2.7</v>
-      </c>
-      <c r="U47">
-        <v>2.88</v>
-      </c>
-      <c r="V47">
-        <v>1.35</v>
-      </c>
       <c r="W47">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA47">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AB47">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC47">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG47">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK47">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q57">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="R57">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U57">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA57">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB57">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC57">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF57">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG57">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q58">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="R58">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S58">
+        <v>1.4</v>
+      </c>
+      <c r="T58">
+        <v>2.58</v>
+      </c>
+      <c r="U58">
+        <v>2.9</v>
+      </c>
+      <c r="V58">
+        <v>1.32</v>
+      </c>
+      <c r="W58">
+        <v>1.04</v>
+      </c>
+      <c r="X58">
+        <v>1.04</v>
+      </c>
+      <c r="Y58">
         <v>1.35</v>
       </c>
-      <c r="T58">
-        <v>2.77</v>
-      </c>
-      <c r="U58">
-        <v>2.65</v>
-      </c>
-      <c r="V58">
-        <v>1.38</v>
-      </c>
-      <c r="W58">
-        <v>1.06</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.28</v>
-      </c>
       <c r="Z58">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA58">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB58">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC58">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AG58">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O59">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q59">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S59">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T59">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="U59">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V59">
+        <v>1.34</v>
+      </c>
+      <c r="W59">
+        <v>1.05</v>
+      </c>
+      <c r="X59">
+        <v>1.03</v>
+      </c>
+      <c r="Y59">
         <v>1.32</v>
       </c>
-      <c r="W59">
-        <v>1.04</v>
-      </c>
-      <c r="X59">
-        <v>1.04</v>
-      </c>
-      <c r="Y59">
-        <v>1.35</v>
-      </c>
       <c r="Z59">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA59">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AB59">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC59">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE59">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG59">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S117">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T117">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U117">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W117">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y117">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z117">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA117">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB117">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC117">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD117">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF117">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG117">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK117">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-27 20:00:00</t>
+          <t>2026-09-27 19:05:00</t>
         </is>
       </c>
     </row>
@@ -19501,153 +19501,479 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N118">
+        <v>2.22</v>
+      </c>
+      <c r="O118">
+        <v>3.54</v>
+      </c>
+      <c r="P118">
+        <v>2.66</v>
+      </c>
+      <c r="Q118">
+        <v>2.72</v>
+      </c>
+      <c r="R118">
+        <v>2.3</v>
+      </c>
+      <c r="S118">
+        <v>1.25</v>
+      </c>
+      <c r="T118">
+        <v>3.8</v>
+      </c>
+      <c r="U118">
+        <v>2.25</v>
+      </c>
+      <c r="V118">
+        <v>1.57</v>
+      </c>
+      <c r="W118">
+        <v>1.11</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.13</v>
+      </c>
+      <c r="Z118">
+        <v>4.6</v>
+      </c>
+      <c r="AA118">
+        <v>1.53</v>
+      </c>
+      <c r="AB118">
+        <v>2.35</v>
+      </c>
+      <c r="AC118">
+        <v>2.3</v>
+      </c>
+      <c r="AD118">
+        <v>1.49</v>
+      </c>
+      <c r="AE118">
+        <v>1.17</v>
+      </c>
+      <c r="AF118">
+        <v>1.44</v>
+      </c>
+      <c r="AG118">
+        <v>2.4</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.2</v>
+      </c>
+      <c r="AK118">
+        <v>1.55</v>
+      </c>
+      <c r="AL118">
+        <v>0</v>
+      </c>
+      <c r="AM118">
+        <v>-1</v>
+      </c>
+      <c r="AN118">
+        <v>-1</v>
+      </c>
+      <c r="AO118">
+        <v>-1</v>
+      </c>
+      <c r="AP118">
+        <v>-1</v>
+      </c>
+      <c r="AQ118">
+        <v>0</v>
+      </c>
+      <c r="AR118">
+        <v>0</v>
+      </c>
+      <c r="AS118">
+        <v>0</v>
+      </c>
+      <c r="AT118">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>2026-09-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>Columbus Crew</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Inter Miami</t>
         </is>
       </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N118">
+      <c r="N119">
         <v>3</v>
       </c>
-      <c r="O118">
+      <c r="O119">
         <v>4.11</v>
       </c>
-      <c r="P118">
+      <c r="P119">
         <v>2.2</v>
       </c>
-      <c r="Q118">
-        <v>0</v>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118">
-        <v>0</v>
-      </c>
-      <c r="U118">
-        <v>0</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
-      <c r="X118">
-        <v>0</v>
-      </c>
-      <c r="Y118">
-        <v>0</v>
-      </c>
-      <c r="Z118">
-        <v>0</v>
-      </c>
-      <c r="AA118">
-        <v>0</v>
-      </c>
-      <c r="AB118">
-        <v>0</v>
-      </c>
-      <c r="AC118">
+      <c r="Q119">
+        <v>0</v>
+      </c>
+      <c r="R119">
+        <v>0</v>
+      </c>
+      <c r="S119">
+        <v>0</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119">
+        <v>0</v>
+      </c>
+      <c r="V119">
+        <v>0</v>
+      </c>
+      <c r="W119">
+        <v>0</v>
+      </c>
+      <c r="X119">
+        <v>0</v>
+      </c>
+      <c r="Y119">
+        <v>0</v>
+      </c>
+      <c r="Z119">
+        <v>0</v>
+      </c>
+      <c r="AA119">
+        <v>0</v>
+      </c>
+      <c r="AB119">
+        <v>0</v>
+      </c>
+      <c r="AC119">
         <v>1.82</v>
       </c>
-      <c r="AD118">
+      <c r="AD119">
         <v>1.85</v>
       </c>
-      <c r="AE118">
-        <v>0</v>
-      </c>
-      <c r="AF118">
-        <v>0</v>
-      </c>
-      <c r="AG118">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>0</v>
-      </c>
-      <c r="AK118">
-        <v>0</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
+      <c r="AE119">
+        <v>0</v>
+      </c>
+      <c r="AF119">
+        <v>0</v>
+      </c>
+      <c r="AG119">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>0</v>
+      </c>
+      <c r="AK119">
+        <v>0</v>
+      </c>
+      <c r="AL119">
+        <v>0</v>
+      </c>
+      <c r="AM119">
+        <v>-1</v>
+      </c>
+      <c r="AN119">
+        <v>-1</v>
+      </c>
+      <c r="AO119">
+        <v>-1</v>
+      </c>
+      <c r="AP119">
+        <v>-1</v>
+      </c>
+      <c r="AQ119">
+        <v>0</v>
+      </c>
+      <c r="AR119">
+        <v>0</v>
+      </c>
+      <c r="AS119">
+        <v>0</v>
+      </c>
+      <c r="AT119">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
         <is>
           <t>2026-09-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+      <c r="S120">
+        <v>0</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120">
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <v>0</v>
+      </c>
+      <c r="W120">
+        <v>0</v>
+      </c>
+      <c r="X120">
+        <v>0</v>
+      </c>
+      <c r="Y120">
+        <v>0</v>
+      </c>
+      <c r="Z120">
+        <v>0</v>
+      </c>
+      <c r="AA120">
+        <v>0</v>
+      </c>
+      <c r="AB120">
+        <v>0</v>
+      </c>
+      <c r="AC120">
+        <v>0</v>
+      </c>
+      <c r="AD120">
+        <v>0</v>
+      </c>
+      <c r="AE120">
+        <v>0</v>
+      </c>
+      <c r="AF120">
+        <v>0</v>
+      </c>
+      <c r="AG120">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>0</v>
+      </c>
+      <c r="AK120">
+        <v>0</v>
+      </c>
+      <c r="AL120">
+        <v>0</v>
+      </c>
+      <c r="AM120">
+        <v>-1</v>
+      </c>
+      <c r="AN120">
+        <v>-1</v>
+      </c>
+      <c r="AO120">
+        <v>-1</v>
+      </c>
+      <c r="AP120">
+        <v>-1</v>
+      </c>
+      <c r="AQ120">
+        <v>0</v>
+      </c>
+      <c r="AR120">
+        <v>0</v>
+      </c>
+      <c r="AS120">
+        <v>0</v>
+      </c>
+      <c r="AT120">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>2026-09-27 22:05:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.38</v>
+        <v>2.39</v>
       </c>
       <c r="O28">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="P28">
-        <v>6.97</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
-        <v>1.75</v>
+        <v>3.04</v>
       </c>
       <c r="R28">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="S28">
         <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U28">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>2.27</v>
+        <v>1.69</v>
       </c>
       <c r="AG28">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>3.12</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.39</v>
+        <v>1.38</v>
       </c>
       <c r="O29">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="P29">
-        <v>2.55</v>
+        <v>6.97</v>
       </c>
       <c r="Q29">
-        <v>3.04</v>
+        <v>1.75</v>
       </c>
       <c r="R29">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="S29">
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK29">
-        <v>1.43</v>
+        <v>3.12</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q36">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U36">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
         <v>1.13</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
+        <v>1.15</v>
+      </c>
+      <c r="Z36">
+        <v>4.6</v>
+      </c>
+      <c r="AA36">
+        <v>1.55</v>
+      </c>
+      <c r="AB36">
+        <v>2.42</v>
+      </c>
+      <c r="AC36">
+        <v>2.33</v>
+      </c>
+      <c r="AD36">
+        <v>1.53</v>
+      </c>
+      <c r="AE36">
         <v>1.18</v>
       </c>
-      <c r="Z36">
-        <v>4.1</v>
-      </c>
-      <c r="AA36">
-        <v>1.68</v>
-      </c>
-      <c r="AB36">
-        <v>2.07</v>
-      </c>
-      <c r="AC36">
-        <v>2.6</v>
-      </c>
-      <c r="AD36">
-        <v>1.43</v>
-      </c>
-      <c r="AE36">
-        <v>1.13</v>
-      </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
         <v>2.1</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD37">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="O100">
-        <v>2.89</v>
+        <v>2.71</v>
       </c>
       <c r="P100">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16642,16 +16642,16 @@
         <v>0</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA100">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB100">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="O101">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P101">
-        <v>2.97</v>
+        <v>4.41</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16805,10 +16805,10 @@
         <v>0</v>
       </c>
       <c r="Y101">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Z101">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA101">
         <v>0</v>
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="O102">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="P102">
-        <v>4.41</v>
+        <v>4.05</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y102">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Z102">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,25 +17098,25 @@
         </is>
       </c>
       <c r="N103">
+        <v>1.76</v>
+      </c>
+      <c r="O103">
+        <v>3.44</v>
+      </c>
+      <c r="P103">
+        <v>4.55</v>
+      </c>
+      <c r="Q103">
+        <v>2.53</v>
+      </c>
+      <c r="R103">
         <v>2.01</v>
       </c>
-      <c r="O103">
-        <v>3.36</v>
-      </c>
-      <c r="P103">
-        <v>4.05</v>
-      </c>
-      <c r="Q103">
-        <v>2.6</v>
-      </c>
-      <c r="R103">
-        <v>2</v>
-      </c>
       <c r="S103">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="U103">
         <v>3.2</v>
@@ -17125,37 +17125,37 @@
         <v>1.3</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z103">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AA103">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB103">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC103">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AD103">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE103">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF103">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG103">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK103">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="O104">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="P104">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="Q104">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z104">
-        <v>2.99</v>
+        <v>2.37</v>
       </c>
       <c r="AA104">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB104">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC104">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-09-27 16:00:00</t>
+          <t>2026-09-27 16:30:00</t>
         </is>
       </c>
     </row>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="O105">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="P105">
-        <v>3.68</v>
+        <v>3.33</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z105">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AA105">
         <v>0</v>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="O106">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="P106">
-        <v>3.33</v>
+        <v>2.83</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17620,10 +17620,10 @@
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z106">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30:00</t>
+          <t>2026-09-27 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,27 +17703,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17783,10 +17783,10 @@
         <v>0</v>
       </c>
       <c r="Y107">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA107">
         <v>0</v>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-09-27 17:00:00</t>
+          <t>2026-09-27 17:30:00</t>
         </is>
       </c>
     </row>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G111">
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18598,10 +18598,10 @@
         <v>0</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-27 17:30:00</t>
+          <t>2026-09-27 18:00:00</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="O113">
-        <v>2.94</v>
+        <v>3.52</v>
       </c>
       <c r="P113">
-        <v>4.32</v>
+        <v>2.74</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="Z113">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="O114">
-        <v>3.52</v>
+        <v>2.95</v>
       </c>
       <c r="P114">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q114">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S114">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T114">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U114">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V114">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W114">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y114">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z114">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AC114">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD114">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE114">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF114">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG114">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK114">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-09-27 18:00:00</t>
+          <t>2026-09-27 18:30:00</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
       <c r="O115">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="P115">
-        <v>3.1</v>
+        <v>5.57</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S116">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T116">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U116">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V116">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W116">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y116">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z116">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA116">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC116">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD116">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE116">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF116">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG116">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK116">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-27 18:30:00</t>
+          <t>2026-09-27 19:05:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-27 19:05:00</t>
+          <t>2026-09-27 20:00:00</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="O118">
-        <v>3.54</v>
+        <v>4.11</v>
       </c>
       <c r="P118">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="Q118">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S118">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T118">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U118">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V118">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z118">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA118">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AD118">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AE118">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF118">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG118">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK118">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="O119">
-        <v>4.11</v>
+        <v>2.89</v>
       </c>
       <c r="P119">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC119">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="AD119">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-27 20:00:00</t>
+          <t>2026-09-27 21:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -7979,55 +7979,55 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>4.82</v>
+        <v>4.34</v>
       </c>
       <c r="Q36">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
         <v>1.13</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AC36">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
         <v>2.1</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.34</v>
+        <v>4.82</v>
       </c>
       <c r="Q37">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U37">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
         <v>1.13</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
+        <v>1.15</v>
+      </c>
+      <c r="Z37">
+        <v>4.6</v>
+      </c>
+      <c r="AA37">
+        <v>1.55</v>
+      </c>
+      <c r="AB37">
+        <v>2.42</v>
+      </c>
+      <c r="AC37">
+        <v>2.33</v>
+      </c>
+      <c r="AD37">
+        <v>1.53</v>
+      </c>
+      <c r="AE37">
         <v>1.18</v>
       </c>
-      <c r="Z37">
-        <v>4.1</v>
-      </c>
-      <c r="AA37">
-        <v>1.68</v>
-      </c>
-      <c r="AB37">
-        <v>2.07</v>
-      </c>
-      <c r="AC37">
-        <v>2.6</v>
-      </c>
-      <c r="AD37">
-        <v>1.43</v>
-      </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q70">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -18900,55 +18900,55 @@
         <v>3.1</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-27 19:05:00</t>
+          <t>2026-09-27 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-09-27 22:05:00</t>
+          <t>2026-09-27 22:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU120"/>
+  <dimension ref="A1:AU119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="G21">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-09-27 15:00:00</t>
+          <t>2026-09-27 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O91">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="P91">
-        <v>2.2</v>
+        <v>2.74</v>
       </c>
       <c r="Q91">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S91">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T91">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U91">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y91">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="Z91">
-        <v>3.42</v>
+        <v>2.15</v>
       </c>
       <c r="AA91">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC91">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD91">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF91">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG91">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK91">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O92">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P92">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15338,10 +15338,10 @@
         <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O93">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P93">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15501,10 +15501,10 @@
         <v>0</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="O94">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="P94">
-        <v>2.66</v>
+        <v>4.42</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15664,10 +15664,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="Z94">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="O95">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="P95">
-        <v>5.19</v>
+        <v>3.07</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="O96">
         <v>3.04</v>
       </c>
       <c r="P96">
-        <v>4.42</v>
+        <v>2.9</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Z96">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="O97">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="P97">
-        <v>3.07</v>
+        <v>3.49</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA97">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AB97">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O98">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="P98">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q98">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S98">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T98">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U98">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V98">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W98">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y98">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z98">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA98">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB98">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC98">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD98">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE98">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF98">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG98">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK98">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-27 15:30:00</t>
+          <t>2026-09-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16399,27 +16399,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="O99">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P99">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="Q99">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S99">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T99">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U99">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V99">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W99">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y99">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z99">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AA99">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AD99">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE99">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF99">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG99">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK99">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-09-27 15:30:00</t>
+          <t>2026-09-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O100">
-        <v>2.71</v>
+        <v>3.36</v>
       </c>
       <c r="P100">
-        <v>2.97</v>
+        <v>4.05</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y100">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z100">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,65 +16772,65 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.76</v>
+      </c>
+      <c r="O101">
+        <v>3.44</v>
+      </c>
+      <c r="P101">
+        <v>4.55</v>
+      </c>
+      <c r="Q101">
+        <v>2.53</v>
+      </c>
+      <c r="R101">
+        <v>2.01</v>
+      </c>
+      <c r="S101">
+        <v>1.4</v>
+      </c>
+      <c r="T101">
+        <v>2.57</v>
+      </c>
+      <c r="U101">
+        <v>3.2</v>
+      </c>
+      <c r="V101">
+        <v>1.3</v>
+      </c>
+      <c r="W101">
+        <v>1.05</v>
+      </c>
+      <c r="X101">
+        <v>1.02</v>
+      </c>
+      <c r="Y101">
+        <v>1.38</v>
+      </c>
+      <c r="Z101">
+        <v>2.99</v>
+      </c>
+      <c r="AA101">
+        <v>2.1</v>
+      </c>
+      <c r="AB101">
+        <v>1.65</v>
+      </c>
+      <c r="AC101">
+        <v>3.74</v>
+      </c>
+      <c r="AD101">
+        <v>1.19</v>
+      </c>
+      <c r="AE101">
+        <v>1.03</v>
+      </c>
+      <c r="AF101">
+        <v>1.9</v>
+      </c>
+      <c r="AG101">
         <v>1.8</v>
       </c>
-      <c r="O101">
-        <v>3.1</v>
-      </c>
-      <c r="P101">
-        <v>4.41</v>
-      </c>
-      <c r="Q101">
-        <v>0</v>
-      </c>
-      <c r="R101">
-        <v>0</v>
-      </c>
-      <c r="S101">
-        <v>0</v>
-      </c>
-      <c r="T101">
-        <v>0</v>
-      </c>
-      <c r="U101">
-        <v>0</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0</v>
-      </c>
-      <c r="X101">
-        <v>0</v>
-      </c>
-      <c r="Y101">
-        <v>1.49</v>
-      </c>
-      <c r="Z101">
-        <v>2.45</v>
-      </c>
-      <c r="AA101">
-        <v>0</v>
-      </c>
-      <c r="AB101">
-        <v>0</v>
-      </c>
-      <c r="AC101">
-        <v>0</v>
-      </c>
-      <c r="AD101">
-        <v>0</v>
-      </c>
-      <c r="AE101">
-        <v>0</v>
-      </c>
-      <c r="AF101">
-        <v>0</v>
-      </c>
-      <c r="AG101">
-        <v>0</v>
-      </c>
       <c r="AH101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O102">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="P102">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="Q102">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z102">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AA102">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC102">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-27 16:00:00</t>
+          <t>2026-09-27 16:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="O103">
-        <v>3.44</v>
+        <v>2.71</v>
       </c>
       <c r="P103">
-        <v>4.55</v>
+        <v>3.33</v>
       </c>
       <c r="Q103">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S103">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T103">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U103">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V103">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W103">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y103">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="Z103">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="AA103">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB103">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC103">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG103">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK103">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-27 16:00:00</t>
+          <t>2026-09-27 16:30:00</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O104">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="P104">
-        <v>3.68</v>
+        <v>2.83</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,10 +17294,10 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z104">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AA104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30:00</t>
+          <t>2026-09-27 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O105">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P105">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30:00</t>
+          <t>2026-09-27 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17620,10 +17620,10 @@
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-27 17:00:00</t>
+          <t>2026-09-27 17:30:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G110">
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-09-27 17:30:00</t>
+          <t>2026-09-27 18:00:00</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="O112">
-        <v>2.94</v>
+        <v>3.52</v>
       </c>
       <c r="P112">
-        <v>4.32</v>
+        <v>2.74</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,81 +18728,81 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="O113">
-        <v>3.52</v>
+        <v>2.95</v>
       </c>
       <c r="P113">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q113">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="R113">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="S113">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="T113">
-        <v>3.38</v>
+        <v>2.55</v>
       </c>
       <c r="U113">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="V113">
+        <v>1.29</v>
+      </c>
+      <c r="W113">
+        <v>1.03</v>
+      </c>
+      <c r="X113">
+        <v>1.02</v>
+      </c>
+      <c r="Y113">
+        <v>1.36</v>
+      </c>
+      <c r="Z113">
+        <v>2.7</v>
+      </c>
+      <c r="AA113">
+        <v>2.2</v>
+      </c>
+      <c r="AB113">
+        <v>1.57</v>
+      </c>
+      <c r="AC113">
+        <v>4.15</v>
+      </c>
+      <c r="AD113">
+        <v>1.16</v>
+      </c>
+      <c r="AE113">
+        <v>1.01</v>
+      </c>
+      <c r="AF113">
+        <v>1.9</v>
+      </c>
+      <c r="AG113">
+        <v>1.78</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <v>1.26</v>
+      </c>
+      <c r="AK113">
         <v>1.53</v>
       </c>
-      <c r="W113">
-        <v>1.12</v>
-      </c>
-      <c r="X113">
-        <v>1.03</v>
-      </c>
-      <c r="Y113">
-        <v>1.14</v>
-      </c>
-      <c r="Z113">
-        <v>4.4</v>
-      </c>
-      <c r="AA113">
-        <v>1.58</v>
-      </c>
-      <c r="AB113">
-        <v>2.24</v>
-      </c>
-      <c r="AC113">
-        <v>2.46</v>
-      </c>
-      <c r="AD113">
-        <v>1.48</v>
-      </c>
-      <c r="AE113">
-        <v>1.14</v>
-      </c>
-      <c r="AF113">
-        <v>1.44</v>
-      </c>
-      <c r="AG113">
-        <v>2.34</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.2</v>
-      </c>
-      <c r="AK113">
-        <v>1.52</v>
-      </c>
       <c r="AL113">
         <v>0</v>
       </c>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-27 18:00:00</t>
+          <t>2026-09-27 18:30:00</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
       <c r="O114">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="P114">
-        <v>3.1</v>
+        <v>5.57</v>
       </c>
       <c r="Q114">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="R114">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="S114">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T114">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="U114">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="V114">
         <v>1.29</v>
       </c>
       <c r="W114">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X114">
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z114">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA114">
         <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC114">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AD114">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE114">
         <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AG114">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK114">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="Q115">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R115">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S115">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T115">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U115">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V115">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W115">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y115">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z115">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA115">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC115">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD115">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE115">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF115">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG115">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK115">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-27 18:30:00</t>
+          <t>2026-09-27 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-27 19:30:00</t>
+          <t>2026-09-27 20:00:00</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="O117">
-        <v>3.54</v>
+        <v>4.11</v>
       </c>
       <c r="P117">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="Q117">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S117">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T117">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U117">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W117">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y117">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z117">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA117">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB117">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC117">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AD117">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF117">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG117">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK117">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="O118">
-        <v>4.11</v>
+        <v>2.89</v>
       </c>
       <c r="P118">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC118">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="AD118">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-27 20:00:00</t>
+          <t>2026-09-27 21:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R119">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S119">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T119">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U119">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V119">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W119">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X119">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z119">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AA119">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB119">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC119">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD119">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE119">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF119">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG119">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK119">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19809,169 +19809,6 @@
         <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
-        <is>
-          <t>2026-09-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Treasure Beach</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120">
-        <v>0</v>
-      </c>
-      <c r="U120">
-        <v>0</v>
-      </c>
-      <c r="V120">
-        <v>0</v>
-      </c>
-      <c r="W120">
-        <v>0</v>
-      </c>
-      <c r="X120">
-        <v>0</v>
-      </c>
-      <c r="Y120">
-        <v>0</v>
-      </c>
-      <c r="Z120">
-        <v>0</v>
-      </c>
-      <c r="AA120">
-        <v>0</v>
-      </c>
-      <c r="AB120">
-        <v>0</v>
-      </c>
-      <c r="AC120">
-        <v>0</v>
-      </c>
-      <c r="AD120">
-        <v>0</v>
-      </c>
-      <c r="AE120">
-        <v>0</v>
-      </c>
-      <c r="AF120">
-        <v>0</v>
-      </c>
-      <c r="AG120">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>0</v>
-      </c>
-      <c r="AK120">
-        <v>0</v>
-      </c>
-      <c r="AL120">
-        <v>0</v>
-      </c>
-      <c r="AM120">
-        <v>-1</v>
-      </c>
-      <c r="AN120">
-        <v>-1</v>
-      </c>
-      <c r="AO120">
-        <v>-1</v>
-      </c>
-      <c r="AP120">
-        <v>-1</v>
-      </c>
-      <c r="AQ120">
-        <v>0</v>
-      </c>
-      <c r="AR120">
-        <v>0</v>
-      </c>
-      <c r="AS120">
-        <v>0</v>
-      </c>
-      <c r="AT120">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
         <is>
           <t>2026-09-27 22:00:00</t>
         </is>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL105">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -19007,7 +19007,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-27 19:30:00</t>
+          <t>2026-09-27 19:05:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q22">
-        <v>5.75</v>
+        <v>2.44</v>
       </c>
       <c r="R22">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T22">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="U22">
-        <v>2.19</v>
+        <v>2.54</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>2.23</v>
+        <v>2.83</v>
       </c>
       <c r="AD22">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.44</v>
+        <v>5.75</v>
       </c>
       <c r="R23">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="S23">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.54</v>
+        <v>2.19</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA23">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="AC23">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK23">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P58">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="U58">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V58">
+        <v>1.34</v>
+      </c>
+      <c r="W58">
+        <v>1.05</v>
+      </c>
+      <c r="X58">
+        <v>1.03</v>
+      </c>
+      <c r="Y58">
         <v>1.32</v>
       </c>
-      <c r="W58">
-        <v>1.04</v>
-      </c>
-      <c r="X58">
-        <v>1.04</v>
-      </c>
-      <c r="Y58">
-        <v>1.35</v>
-      </c>
       <c r="Z58">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AB58">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC58">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD58">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE58">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG58">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK58">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O59">
         <v>3.2</v>
       </c>
       <c r="P59">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q59">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S59">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V59">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB59">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC59">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF59">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG59">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK59">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="O60">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P60">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB60">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O61">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P61">
         <v>3.4</v>
@@ -10291,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB61">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O62">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O63">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="P63">
-        <v>4.33</v>
+        <v>2.39</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA63">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB63">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00:00</t>
+          <t>2026-09-27 12:30:00</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="O64">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="Q64">
-        <v>3.58</v>
+        <v>4.18</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S64">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U64">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V64">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
         <v>1</v>
       </c>
       <c r="Y64">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA64">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB64">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC64">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD64">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
         <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG64">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.29</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q65">
-        <v>4.18</v>
+        <v>2.62</v>
       </c>
       <c r="R65">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="U65">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V65">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W65">
         <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z65">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AA65">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AB65">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC65">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE65">
         <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AG65">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="AL65">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="O4">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="P4">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB4">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="O5">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="P6">
-        <v>3.53</v>
+        <v>5.21</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P15">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="O16">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="P16">
-        <v>3.02</v>
+        <v>4.03</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P17">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,49 +5688,49 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O33">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="P33">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="Q33">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="R33">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
         <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
         <v>3.28</v>
@@ -5739,13 +5739,13 @@
         <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AG33">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK33">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB38">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P51">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P52">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB52">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="O53">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="P53">
         <v>11</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB54">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="O55">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P55">
-        <v>3.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P59">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="O60">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P60">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB60">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="O61">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="P61">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P62">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB62">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -11402,22 +11402,22 @@
         <v>2.49</v>
       </c>
       <c r="Q68">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="R68">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U68">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V68">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
         <v>1.07</v>
@@ -11426,22 +11426,22 @@
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z68">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA68">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB68">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC68">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD68">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE68">
         <v>1.04</v>
@@ -11450,7 +11450,7 @@
         <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK68">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="Q69">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="R69">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S69">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T69">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U69">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="V69">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z69">
-        <v>2.62</v>
+        <v>3.31</v>
       </c>
       <c r="AA69">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB69">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC69">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD69">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG69">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -16129,19 +16129,19 @@
         <v>3.49</v>
       </c>
       <c r="Q97">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R97">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S97">
         <v>1.4</v>
       </c>
       <c r="T97">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="U97">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V97">
         <v>1.3</v>
@@ -16150,34 +16150,34 @@
         <v>1.01</v>
       </c>
       <c r="X97">
+        <v>1.02</v>
+      </c>
+      <c r="Y97">
+        <v>1.35</v>
+      </c>
+      <c r="Z97">
+        <v>2.74</v>
+      </c>
+      <c r="AA97">
+        <v>2.28</v>
+      </c>
+      <c r="AB97">
+        <v>1.61</v>
+      </c>
+      <c r="AC97">
+        <v>4.1</v>
+      </c>
+      <c r="AD97">
+        <v>1.16</v>
+      </c>
+      <c r="AE97">
         <v>1.01</v>
       </c>
-      <c r="Y97">
-        <v>1.33</v>
-      </c>
-      <c r="Z97">
-        <v>2.83</v>
-      </c>
-      <c r="AA97">
-        <v>2.11</v>
-      </c>
-      <c r="AB97">
-        <v>1.62</v>
-      </c>
-      <c r="AC97">
-        <v>3.88</v>
-      </c>
-      <c r="AD97">
-        <v>1.18</v>
-      </c>
-      <c r="AE97">
-        <v>1.02</v>
-      </c>
       <c r="AF97">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG97">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK97">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q115">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>5.2</v>
+        <v>4.85</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="U2">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.35</v>
+      </c>
+      <c r="Z2">
+        <v>2.74</v>
+      </c>
+      <c r="AA2">
+        <v>2.25</v>
+      </c>
+      <c r="AB2">
+        <v>1.66</v>
+      </c>
+      <c r="AC2">
+        <v>3.92</v>
+      </c>
+      <c r="AD2">
+        <v>1.18</v>
+      </c>
+      <c r="AE2">
         <v>1.02</v>
       </c>
-      <c r="Y2">
-        <v>1.33</v>
-      </c>
-      <c r="Z2">
-        <v>2.97</v>
-      </c>
-      <c r="AA2">
-        <v>2.08</v>
-      </c>
-      <c r="AB2">
-        <v>1.72</v>
-      </c>
-      <c r="AC2">
-        <v>3.5</v>
-      </c>
-      <c r="AD2">
-        <v>1.26</v>
-      </c>
-      <c r="AE2">
-        <v>1.04</v>
-      </c>
       <c r="AF2">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG2">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="AK2">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>3</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R7">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AB7">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AC7">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q8">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S8">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="U8">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA8">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC8">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AD8">
+        <v>1.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.08</v>
+      </c>
+      <c r="AF8">
+        <v>1.73</v>
+      </c>
+      <c r="AG8">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.25</v>
       </c>
-      <c r="AE8">
-        <v>1.06</v>
-      </c>
-      <c r="AF8">
-        <v>1.77</v>
-      </c>
-      <c r="AG8">
-        <v>1.89</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.23</v>
-      </c>
       <c r="AK8">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,52 +1776,52 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="P9">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="Q9">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R9">
         <v>1.92</v>
       </c>
       <c r="S9">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U9">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AA9">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AB9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC9">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD9">
         <v>1.18</v>
@@ -1830,7 +1830,7 @@
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
         <v>1.69</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>1.85</v>
       </c>
       <c r="Q14">
-        <v>4.72</v>
+        <v>5.2</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S14">
         <v>1.38</v>
@@ -2612,13 +2612,13 @@
         <v>2.65</v>
       </c>
       <c r="U14">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="V14">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.05</v>
@@ -2627,41 +2627,41 @@
         <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA14">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC14">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AD14">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
         <v>1.05</v>
       </c>
       <c r="AF14">
+        <v>1.95</v>
+      </c>
+      <c r="AG14">
+        <v>1.75</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.87</v>
-      </c>
-      <c r="AG14">
-        <v>1.77</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.3</v>
       </c>
       <c r="AK14">
         <v>1.17</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O19">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="P19">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
         <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S20">
         <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
+        <v>1.06</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.35</v>
+      </c>
+      <c r="Z20">
+        <v>2.88</v>
+      </c>
+      <c r="AA20">
+        <v>2.25</v>
+      </c>
+      <c r="AB20">
+        <v>1.59</v>
+      </c>
+      <c r="AC20">
+        <v>4.05</v>
+      </c>
+      <c r="AD20">
+        <v>1.16</v>
+      </c>
+      <c r="AE20">
         <v>1.01</v>
       </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.31</v>
-      </c>
-      <c r="Z20">
-        <v>2.92</v>
-      </c>
-      <c r="AA20">
-        <v>2.08</v>
-      </c>
-      <c r="AB20">
-        <v>1.64</v>
-      </c>
-      <c r="AC20">
-        <v>3.8</v>
-      </c>
-      <c r="AD20">
-        <v>1.19</v>
-      </c>
-      <c r="AE20">
-        <v>1.02</v>
-      </c>
       <c r="AF20">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3904,25 +3904,25 @@
         <v>3.64</v>
       </c>
       <c r="Q22">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R22">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3934,10 +3934,10 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
         <v>2.83</v>
@@ -3946,13 +3946,13 @@
         <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>2.55</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U23">
         <v>2.19</v>
@@ -4085,7 +4085,7 @@
         <v>1.63</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4109,13 +4109,13 @@
         <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF23">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="Q25">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R25">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S25">
         <v>1.35</v>
@@ -4411,7 +4411,7 @@
         <v>1.41</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4423,10 +4423,10 @@
         <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>2.81</v>
@@ -4438,10 +4438,10 @@
         <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O26">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="P26">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q26">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="R26">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4568,31 +4568,31 @@
         <v>3</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
         <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
         <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD26">
         <v>1.33</v>
@@ -4601,26 +4601,26 @@
         <v>1.1</v>
       </c>
       <c r="AF26">
+        <v>1.65</v>
+      </c>
+      <c r="AG26">
+        <v>2.13</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.31</v>
+      </c>
+      <c r="AK26">
         <v>1.62</v>
-      </c>
-      <c r="AG26">
-        <v>2.15</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.34</v>
-      </c>
-      <c r="AK26">
-        <v>1.63</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,22 +4719,22 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R27">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U27">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="V27">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4743,31 +4743,31 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA27">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB27">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="AC27">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AD27">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.39</v>
+        <v>1.36</v>
       </c>
       <c r="O28">
-        <v>3.22</v>
+        <v>4.33</v>
       </c>
       <c r="P28">
-        <v>2.55</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>3.04</v>
+        <v>1.8</v>
       </c>
       <c r="R28">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
         <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U28">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
         <v>1.08</v>
@@ -4906,31 +4906,31 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC28">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="O29">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
-        <v>6.97</v>
+        <v>2.8</v>
       </c>
       <c r="Q29">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="R29">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
         <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC29">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AD29">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE29">
         <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>3.12</v>
+        <v>1.57</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O32">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P32">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q32">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="R32">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="S32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T32">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="U32">
         <v>1.75</v>
       </c>
       <c r="V32">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="W32">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.03</v>
       </c>
       <c r="Z32">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA32">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AB32">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AC32">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AD32">
         <v>2.12</v>
       </c>
       <c r="AE32">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AF32">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AG32">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6186,46 +6186,46 @@
         <v>4.34</v>
       </c>
       <c r="Q36">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB36">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AC36">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6367,31 +6367,31 @@
         <v>1.6</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB37">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AC37">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD37">
         <v>1.53</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
         <v>1.53</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="O39">
         <v>3.9</v>
       </c>
       <c r="P39">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Q39">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="R39">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="AD39">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="O43">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P43">
-        <v>5.54</v>
+        <v>6.4</v>
       </c>
       <c r="Q43">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="R43">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="S43">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="U43">
         <v>2.88</v>
@@ -7348,7 +7348,7 @@
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y43">
         <v>1.35</v>
@@ -7357,13 +7357,13 @@
         <v>2.97</v>
       </c>
       <c r="AA43">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB43">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC43">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD43">
         <v>1.19</v>
@@ -7372,10 +7372,10 @@
         <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG43">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="O45">
         <v>3.25</v>
       </c>
       <c r="P45">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q45">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="R45">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="S45">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T45">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="U45">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V45">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.33</v>
+      </c>
+      <c r="Z45">
+        <v>3.1</v>
+      </c>
+      <c r="AA45">
+        <v>2.01</v>
+      </c>
+      <c r="AB45">
+        <v>1.7</v>
+      </c>
+      <c r="AC45">
+        <v>3.8</v>
+      </c>
+      <c r="AD45">
+        <v>1.22</v>
+      </c>
+      <c r="AE45">
         <v>1.05</v>
       </c>
-      <c r="Y45">
-        <v>1.39</v>
-      </c>
-      <c r="Z45">
-        <v>2.59</v>
-      </c>
-      <c r="AA45">
-        <v>2.24</v>
-      </c>
-      <c r="AB45">
-        <v>1.55</v>
-      </c>
-      <c r="AC45">
-        <v>4.15</v>
-      </c>
-      <c r="AD45">
-        <v>1.16</v>
-      </c>
-      <c r="AE45">
-        <v>1.03</v>
-      </c>
       <c r="AF45">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="O46">
         <v>3.25</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q46">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="R46">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="S46">
+        <v>1.43</v>
+      </c>
+      <c r="T46">
+        <v>2.48</v>
+      </c>
+      <c r="U46">
+        <v>3</v>
+      </c>
+      <c r="V46">
+        <v>1.3</v>
+      </c>
+      <c r="W46">
+        <v>1.03</v>
+      </c>
+      <c r="X46">
+        <v>1.05</v>
+      </c>
+      <c r="Y46">
         <v>1.39</v>
       </c>
-      <c r="T46">
-        <v>2.61</v>
-      </c>
-      <c r="U46">
-        <v>2.81</v>
-      </c>
-      <c r="V46">
-        <v>1.36</v>
-      </c>
-      <c r="W46">
-        <v>1.05</v>
-      </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.33</v>
-      </c>
       <c r="Z46">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AA46">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="AB46">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC46">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AD46">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AG46">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>5.46</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S47">
         <v>1.41</v>
@@ -8000,7 +8000,7 @@
         <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
         <v>1.3</v>
@@ -8009,25 +8009,25 @@
         <v>3.25</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB47">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC47">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD47">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG47">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q48">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V48">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
         <v>1.05</v>
@@ -8169,28 +8169,28 @@
         <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA48">
         <v>1.9</v>
       </c>
       <c r="AB48">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC48">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE48">
         <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG48">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -10587,71 +10587,71 @@
         <v>2.39</v>
       </c>
       <c r="Q63">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U63">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V63">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W63">
+        <v>1.07</v>
+      </c>
+      <c r="X63">
+        <v>1.01</v>
+      </c>
+      <c r="Y63">
+        <v>1.35</v>
+      </c>
+      <c r="Z63">
+        <v>2.88</v>
+      </c>
+      <c r="AA63">
+        <v>2.1</v>
+      </c>
+      <c r="AB63">
+        <v>1.63</v>
+      </c>
+      <c r="AC63">
+        <v>3.86</v>
+      </c>
+      <c r="AD63">
+        <v>1.18</v>
+      </c>
+      <c r="AE63">
         <v>1.02</v>
       </c>
-      <c r="X63">
-        <v>1</v>
-      </c>
-      <c r="Y63">
+      <c r="AF63">
+        <v>1.8</v>
+      </c>
+      <c r="AG63">
+        <v>1.85</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.3</v>
       </c>
-      <c r="Z63">
-        <v>2.97</v>
-      </c>
-      <c r="AA63">
-        <v>2.02</v>
-      </c>
-      <c r="AB63">
-        <v>1.68</v>
-      </c>
-      <c r="AC63">
-        <v>3.58</v>
-      </c>
-      <c r="AD63">
-        <v>1.21</v>
-      </c>
-      <c r="AE63">
-        <v>1.03</v>
-      </c>
-      <c r="AF63">
-        <v>1.78</v>
-      </c>
-      <c r="AG63">
-        <v>1.89</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.25</v>
-      </c>
       <c r="AK63">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,25 +10750,25 @@
         <v>2.03</v>
       </c>
       <c r="Q64">
-        <v>4.18</v>
+        <v>4.34</v>
       </c>
       <c r="R64">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T64">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
         <v>1</v>
@@ -10780,10 +10780,10 @@
         <v>3.05</v>
       </c>
       <c r="AA64">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB64">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC64">
         <v>3.5</v>
@@ -10795,10 +10795,10 @@
         <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,52 +11067,52 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O66">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="Q66">
         <v>2.3</v>
       </c>
       <c r="R66">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
         <v>1.41</v>
       </c>
       <c r="T66">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U66">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V66">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z66">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB66">
         <v>1.64</v>
       </c>
       <c r="AC66">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AD66">
         <v>1.19</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
         <v>1.91</v>
@@ -11239,55 +11239,55 @@
         <v>2.76</v>
       </c>
       <c r="Q67">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R67">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="U67">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="V67">
         <v>1.5</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z67">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA67">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB67">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AC67">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD67">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11888,10 +11888,10 @@
         <v>4</v>
       </c>
       <c r="P71">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q71">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="R71">
         <v>2.16</v>
@@ -11939,7 +11939,7 @@
         <v>2.14</v>
       </c>
       <c r="AG71">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12543,71 +12543,71 @@
         <v>2.82</v>
       </c>
       <c r="Q75">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="R75">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S75">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="T75">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="U75">
-        <v>2.86</v>
+        <v>3.06</v>
       </c>
       <c r="V75">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W75">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X75">
         <v>1.05</v>
       </c>
       <c r="Y75">
+        <v>1.4</v>
+      </c>
+      <c r="Z75">
+        <v>2.56</v>
+      </c>
+      <c r="AA75">
+        <v>2.23</v>
+      </c>
+      <c r="AB75">
+        <v>1.56</v>
+      </c>
+      <c r="AC75">
+        <v>4.2</v>
+      </c>
+      <c r="AD75">
+        <v>1.17</v>
+      </c>
+      <c r="AE75">
+        <v>1.03</v>
+      </c>
+      <c r="AF75">
+        <v>2</v>
+      </c>
+      <c r="AG75">
+        <v>1.7</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.33</v>
       </c>
-      <c r="Z75">
-        <v>2.83</v>
-      </c>
-      <c r="AA75">
-        <v>2.08</v>
-      </c>
-      <c r="AB75">
-        <v>1.64</v>
-      </c>
-      <c r="AC75">
-        <v>3.68</v>
-      </c>
-      <c r="AD75">
-        <v>1.2</v>
-      </c>
-      <c r="AE75">
-        <v>1.05</v>
-      </c>
-      <c r="AF75">
-        <v>1.82</v>
-      </c>
-      <c r="AG75">
-        <v>1.82</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.26</v>
-      </c>
       <c r="AK75">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O79">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB79">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O80">
+        <v>3.3</v>
+      </c>
+      <c r="P80">
+        <v>3.7</v>
+      </c>
+      <c r="Q80">
+        <v>2.6</v>
+      </c>
+      <c r="R80">
+        <v>1.97</v>
+      </c>
+      <c r="S80">
+        <v>1.44</v>
+      </c>
+      <c r="T80">
+        <v>2.5</v>
+      </c>
+      <c r="U80">
         <v>3</v>
       </c>
-      <c r="P80">
-        <v>3</v>
-      </c>
-      <c r="Q80">
-        <v>3.1</v>
-      </c>
-      <c r="R80">
-        <v>1.91</v>
-      </c>
-      <c r="S80">
-        <v>1.43</v>
-      </c>
-      <c r="T80">
-        <v>2.48</v>
-      </c>
-      <c r="U80">
-        <v>3.06</v>
-      </c>
       <c r="V80">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W80">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z80">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AA80">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AB80">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC80">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AD80">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF80">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG80">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,34 +13512,34 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="O81">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q81">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S81">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T81">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U81">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V81">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13551,22 +13551,22 @@
         <v>3.14</v>
       </c>
       <c r="AA81">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB81">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AC81">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD81">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE81">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG81">
         <v>1.84</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK81">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O82">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="P82">
-        <v>3.91</v>
+        <v>3.6</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S82">
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="U82">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V82">
         <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA82">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB82">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC82">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE82">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF82">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG82">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14656,61 +14656,61 @@
         <v>1.91</v>
       </c>
       <c r="O88">
+        <v>3.85</v>
+      </c>
+      <c r="P88">
+        <v>3.2</v>
+      </c>
+      <c r="Q88">
+        <v>2.41</v>
+      </c>
+      <c r="R88">
+        <v>2.34</v>
+      </c>
+      <c r="S88">
+        <v>1.22</v>
+      </c>
+      <c r="T88">
         <v>3.8</v>
       </c>
-      <c r="P88">
-        <v>3.1</v>
-      </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <v>0</v>
-      </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <v>0</v>
-      </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA88">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB88">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>4.2</v>
       </c>
       <c r="Q89">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="R89">
         <v>1.86</v>
@@ -14852,13 +14852,13 @@
         <v>1.5</v>
       </c>
       <c r="Z89">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AA89">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AB89">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC89">
         <v>4.75</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O90">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
         <v>2.2</v>
       </c>
       <c r="Q90">
-        <v>3.76</v>
+        <v>3.27</v>
       </c>
       <c r="R90">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S90">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T90">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="U90">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="AA90">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AB90">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AC90">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="AD90">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF90">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AG90">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="O95">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P95">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB95">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15957,34 +15957,34 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="O96">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="Q96">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R96">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="S96">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T96">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U96">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V96">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
         <v>1.03</v>
@@ -15993,25 +15993,25 @@
         <v>1.36</v>
       </c>
       <c r="Z96">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA96">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AB96">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC96">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AD96">
         <v>1.18</v>
       </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF96">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG96">
         <v>1.8</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O100">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="P100">
-        <v>4.05</v>
+        <v>3.86</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
@@ -16624,10 +16624,10 @@
         <v>2</v>
       </c>
       <c r="S100">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T100">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="U100">
         <v>3.2</v>
@@ -16636,7 +16636,7 @@
         <v>1.3</v>
       </c>
       <c r="W100">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X100">
         <v>1.1</v>
@@ -16645,13 +16645,13 @@
         <v>1.36</v>
       </c>
       <c r="Z100">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA100">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AB100">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC100">
         <v>4</v>
@@ -16660,10 +16660,10 @@
         <v>1.17</v>
       </c>
       <c r="AE100">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF100">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG100">
         <v>1.7</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK100">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,25 +16772,25 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="O101">
-        <v>3.44</v>
+        <v>2.98</v>
       </c>
       <c r="P101">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q101">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="R101">
         <v>2.01</v>
       </c>
       <c r="S101">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T101">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U101">
         <v>3.2</v>
@@ -16805,22 +16805,22 @@
         <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z101">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="AA101">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB101">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC101">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD101">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE101">
         <v>1.03</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="O105">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P105">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q105">
         <v>3.32</v>
@@ -18574,16 +18574,16 @@
         <v>2.74</v>
       </c>
       <c r="Q112">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R112">
         <v>2.38</v>
       </c>
       <c r="S112">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T112">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U112">
         <v>2.29</v>
@@ -18595,7 +18595,7 @@
         <v>1.12</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
         <v>1.14</v>
@@ -18607,16 +18607,16 @@
         <v>1.58</v>
       </c>
       <c r="AB112">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AC112">
         <v>2.46</v>
       </c>
       <c r="AD112">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE112">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF112">
         <v>1.44</v>
@@ -18737,55 +18737,55 @@
         <v>3.1</v>
       </c>
       <c r="Q113">
+        <v>3.28</v>
+      </c>
+      <c r="R113">
+        <v>1.83</v>
+      </c>
+      <c r="S113">
+        <v>1.4</v>
+      </c>
+      <c r="T113">
+        <v>2.7</v>
+      </c>
+      <c r="U113">
         <v>2.9</v>
       </c>
-      <c r="R113">
-        <v>1.94</v>
-      </c>
-      <c r="S113">
-        <v>1.41</v>
-      </c>
-      <c r="T113">
-        <v>2.55</v>
-      </c>
-      <c r="U113">
-        <v>3.06</v>
-      </c>
       <c r="V113">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W113">
+        <v>1.07</v>
+      </c>
+      <c r="X113">
         <v>1.03</v>
       </c>
-      <c r="X113">
-        <v>1.02</v>
-      </c>
       <c r="Y113">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z113">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA113">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB113">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC113">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AD113">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF113">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG113">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK113">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,16 +18891,16 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O114">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P114">
-        <v>5.57</v>
+        <v>5.1</v>
       </c>
       <c r="Q114">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="R114">
         <v>1.99</v>
@@ -18927,13 +18927,13 @@
         <v>1.35</v>
       </c>
       <c r="Z114">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AA114">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB114">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC114">
         <v>4</v>
@@ -18945,10 +18945,10 @@
         <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AG114">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.14</v>
       </c>
       <c r="AK114">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19226,13 +19226,13 @@
         <v>2.66</v>
       </c>
       <c r="Q116">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="R116">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S116">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T116">
         <v>3.8</v>
@@ -19241,7 +19241,7 @@
         <v>2.25</v>
       </c>
       <c r="V116">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W116">
         <v>1.11</v>
@@ -19253,28 +19253,28 @@
         <v>1.13</v>
       </c>
       <c r="Z116">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA116">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB116">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC116">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD116">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE116">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF116">
         <v>1.44</v>
       </c>
       <c r="AG116">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK116">
         <v>1.55</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -638,61 +638,61 @@
         <v>3.3</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
+        <v>1.98</v>
+      </c>
+      <c r="Q2">
+        <v>4.82</v>
+      </c>
+      <c r="R2">
         <v>1.94</v>
       </c>
-      <c r="Q2">
-        <v>4.85</v>
-      </c>
-      <c r="R2">
-        <v>1.97</v>
-      </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="U2">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V2">
         <v>1.31</v>
       </c>
       <c r="W2">
+        <v>1.03</v>
+      </c>
+      <c r="X2">
         <v>1.04</v>
       </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
       <c r="Y2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AG2">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AK2">
         <v>1.22</v>
@@ -7327,22 +7327,22 @@
         <v>6.4</v>
       </c>
       <c r="Q43">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="R43">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
+        <v>1.35</v>
+      </c>
+      <c r="T43">
+        <v>2.82</v>
+      </c>
+      <c r="U43">
+        <v>2.83</v>
+      </c>
+      <c r="V43">
         <v>1.36</v>
-      </c>
-      <c r="T43">
-        <v>2.83</v>
-      </c>
-      <c r="U43">
-        <v>2.88</v>
-      </c>
-      <c r="V43">
-        <v>1.35</v>
       </c>
       <c r="W43">
         <v>1.04</v>
@@ -7351,31 +7351,31 @@
         <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z43">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA43">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC43">
-        <v>3.78</v>
+        <v>3.58</v>
       </c>
       <c r="AD43">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG43">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="O63">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>4.34</v>
       </c>
       <c r="R63">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U63">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W63">
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z63">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA63">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC63">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AD63">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG63">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK63">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.29</v>
+        <v>2.6</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P64">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="Q64">
-        <v>4.34</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U64">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V64">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W64">
         <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z64">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA64">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB64">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC64">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AD64">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE64">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF64">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL64">
         <v>0</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -644,7 +644,7 @@
         <v>1.98</v>
       </c>
       <c r="Q2">
-        <v>4.82</v>
+        <v>4.9</v>
       </c>
       <c r="R2">
         <v>1.94</v>
@@ -674,10 +674,10 @@
         <v>2.62</v>
       </c>
       <c r="AA2">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
         <v>4.15</v>
@@ -1465,13 +1465,13 @@
         <v>2.05</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1480,7 +1480,7 @@
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.26</v>
@@ -1489,10 +1489,10 @@
         <v>3.2</v>
       </c>
       <c r="AA7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
         <v>3.34</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,55 +1613,55 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U8">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA8">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB8">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC8">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
         <v>1.08</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2600,25 +2600,25 @@
         <v>1.85</v>
       </c>
       <c r="Q14">
-        <v>5.2</v>
+        <v>5.26</v>
       </c>
       <c r="R14">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V14">
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.05</v>
@@ -3946,7 +3946,7 @@
         <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
         <v>1.65</v>
@@ -4067,25 +4067,25 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4097,13 +4097,13 @@
         <v>4.55</v>
       </c>
       <c r="AA23">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AC23">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AD23">
         <v>1.55</v>
@@ -4112,7 +4112,7 @@
         <v>1.21</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
         <v>2.2</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4387,77 +4387,77 @@
         <v>1.9</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
         <v>3.34</v>
       </c>
       <c r="Q25">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="R25">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U25">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
+        <v>1.2</v>
+      </c>
+      <c r="Z25">
+        <v>3.72</v>
+      </c>
+      <c r="AA25">
+        <v>1.7</v>
+      </c>
+      <c r="AB25">
+        <v>2</v>
+      </c>
+      <c r="AC25">
+        <v>2.66</v>
+      </c>
+      <c r="AD25">
+        <v>1.4</v>
+      </c>
+      <c r="AE25">
+        <v>1.12</v>
+      </c>
+      <c r="AF25">
+        <v>1.6</v>
+      </c>
+      <c r="AG25">
+        <v>2.11</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.22</v>
       </c>
-      <c r="Z25">
-        <v>3.5</v>
-      </c>
-      <c r="AA25">
-        <v>1.77</v>
-      </c>
-      <c r="AB25">
-        <v>1.9</v>
-      </c>
-      <c r="AC25">
-        <v>2.81</v>
-      </c>
-      <c r="AD25">
-        <v>1.33</v>
-      </c>
-      <c r="AE25">
-        <v>1.1</v>
-      </c>
-      <c r="AF25">
-        <v>1.65</v>
-      </c>
-      <c r="AG25">
-        <v>2.03</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.23</v>
-      </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>4.8</v>
+        <v>4.38</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O33">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
         <v>7.5</v>
@@ -5700,7 +5700,7 @@
         <v>1.8</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S33">
         <v>1.36</v>
@@ -5709,10 +5709,10 @@
         <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <v>1.07</v>
@@ -5721,22 +5721,22 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA33">
         <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC33">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
         <v>1.06</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK33">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6720,10 +6720,10 @@
         <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O43">
         <v>3.56</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="O45">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
         <v>3.3</v>
@@ -7665,10 +7665,10 @@
         <v>2.61</v>
       </c>
       <c r="U45">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W45">
         <v>1.05</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>2.13</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P46">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="Q46">
         <v>2.72</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.29</v>
+        <v>2.6</v>
       </c>
       <c r="O63">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P63">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="Q63">
-        <v>4.34</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U63">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V63">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W63">
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z63">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA63">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB63">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC63">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AD63">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG63">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="O64">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>4.34</v>
       </c>
       <c r="R64">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T64">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W64">
         <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA64">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB64">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC64">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AD64">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11402,16 +11402,16 @@
         <v>2.49</v>
       </c>
       <c r="Q68">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S68">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T68">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="U68">
         <v>2.88</v>
@@ -11420,31 +11420,31 @@
         <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z68">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA68">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB68">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AD68">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
         <v>1.75</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="O69">
         <v>3</v>
@@ -11565,10 +11565,10 @@
         <v>2.87</v>
       </c>
       <c r="Q69">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S69">
         <v>1.37</v>
@@ -11583,7 +11583,7 @@
         <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11595,25 +11595,25 @@
         <v>3.31</v>
       </c>
       <c r="AA69">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AB69">
         <v>1.68</v>
       </c>
       <c r="AC69">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
         <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG69">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,16 +11882,16 @@
         </is>
       </c>
       <c r="N71">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P71">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Q71">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="R71">
         <v>2.16</v>
@@ -11936,10 +11936,10 @@
         <v>1.09</v>
       </c>
       <c r="AF71">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG71">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK71">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12555,10 +12555,10 @@
         <v>2.39</v>
       </c>
       <c r="U75">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W75">
         <v>1.02</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13868,7 +13868,7 @@
         <v>1.04</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
         <v>1.33</v>
@@ -13889,7 +13889,7 @@
         <v>1.2</v>
       </c>
       <c r="AE83">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
         <v>1.85</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O89">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P89">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="Q89">
         <v>2.56</v>
@@ -14867,7 +14867,7 @@
         <v>1.12</v>
       </c>
       <c r="AE89">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF89">
         <v>2.19</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
         <v>1.79</v>
@@ -16132,7 +16132,7 @@
         <v>2.62</v>
       </c>
       <c r="R97">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S97">
         <v>1.4</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK97">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="O105">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P105">
         <v>3.1</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK105">
         <v>1.42</v>

--- a/jogos_2026-09-27.xlsx
+++ b/jogos_2026-09-27.xlsx
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -929,96 +929,96 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="O4">
-        <v>3.09</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA4">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AB4">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1027,41 +1027,41 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "72"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1092,139 +1092,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="O5">
         <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA5">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB5">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>["7", "57"]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1255,25 +1255,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1283,111 +1283,111 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>3.61</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>5.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA6">
+        <v>2.2</v>
+      </c>
+      <c r="AB6">
+        <v>1.62</v>
+      </c>
+      <c r="AC6">
+        <v>3.88</v>
+      </c>
+      <c r="AD6">
+        <v>1.18</v>
+      </c>
+      <c r="AE6">
+        <v>1.03</v>
+      </c>
+      <c r="AF6">
+        <v>1.85</v>
+      </c>
+      <c r="AG6">
+        <v>1.85</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>["39"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>["28"]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.27</v>
+      </c>
+      <c r="AK6">
+        <v>1.41</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>2</v>
       </c>
-      <c r="AB6">
-        <v>1.8</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
         <v>2.68</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
@@ -1652,7 +1652,7 @@
         <v>3.28</v>
       </c>
       <c r="AA8">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
         <v>1.87</v>
@@ -1664,7 +1664,7 @@
         <v>1.28</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
         <v>1.73</v>
@@ -1686,7 +1686,7 @@
         <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
         <v>3.5</v>
       </c>
       <c r="Q10">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="R10">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1972,28 +1972,28 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC10">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
         <v>1.85</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="O12">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.98</v>
+        <v>2.94</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>1.85</v>
       </c>
       <c r="Q14">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="R14">
         <v>2.02</v>
@@ -2636,10 +2636,10 @@
         <v>1.63</v>
       </c>
       <c r="AC14">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE14">
         <v>1.05</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AK14">
         <v>1.17</v>
@@ -2731,130 +2731,130 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="O15">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA15">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "77", "85"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "28", "88"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,16 +2885,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2913,17 +2913,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>4.03</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>["-1"]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ16">
         <v>0</v>
       </c>
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,139 +3048,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="O17">
+        <v>3.2</v>
+      </c>
+      <c r="P17">
+        <v>3.8</v>
+      </c>
+      <c r="Q17">
+        <v>2.38</v>
+      </c>
+      <c r="R17">
+        <v>2.08</v>
+      </c>
+      <c r="S17">
+        <v>1.4</v>
+      </c>
+      <c r="T17">
+        <v>2.8</v>
+      </c>
+      <c r="U17">
+        <v>2.9</v>
+      </c>
+      <c r="V17">
+        <v>1.36</v>
+      </c>
+      <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
         <v>3.08</v>
       </c>
-      <c r="P17">
-        <v>3.24</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "45+1"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3421,16 +3421,16 @@
         <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
         <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
         <v>1.1</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>2.75</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q20">
         <v>3.4</v>
@@ -3584,49 +3584,49 @@
         <v>2</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U20">
+        <v>2.88</v>
+      </c>
+      <c r="V20">
+        <v>1.36</v>
+      </c>
+      <c r="W20">
+        <v>1.07</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.3</v>
+      </c>
+      <c r="Z20">
         <v>3</v>
       </c>
-      <c r="V20">
-        <v>1.33</v>
-      </c>
-      <c r="W20">
-        <v>1.06</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.35</v>
-      </c>
-      <c r="Z20">
-        <v>2.88</v>
-      </c>
       <c r="AA20">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AC20">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="AD20">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3741,98 +3741,98 @@
         <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "90"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R23">
         <v>2.6</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>3.53</v>
+        <v>2.85</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O26">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P26">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q26">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
         <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG26">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="S27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z27">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AB27">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AD27">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
         <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG27">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>2.58</v>
+        <v>2.27</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O28">
         <v>4.33</v>
@@ -4882,25 +4882,25 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4912,16 +4912,16 @@
         <v>3.58</v>
       </c>
       <c r="AA28">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD28">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE28">
         <v>1.1</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AK28">
         <v>2.9</v>
@@ -5039,19 +5039,19 @@
         <v>2.15</v>
       </c>
       <c r="O29">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q29">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="R29">
         <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T29">
         <v>3.2</v>
@@ -5060,10 +5060,10 @@
         <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.03</v>
@@ -5090,10 +5090,10 @@
         <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
         <v>1.57</v>
@@ -5339,16 +5339,16 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -5358,77 +5358,77 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="Q31">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AB31">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AD31">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,13 +5502,13 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -5521,20 +5521,20 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="Q32">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="R32">
         <v>2.63</v>
@@ -5543,13 +5543,13 @@
         <v>1.13</v>
       </c>
       <c r="T32">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="U32">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V32">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="W32">
         <v>1.28</v>
@@ -5561,71 +5561,71 @@
         <v>1.03</v>
       </c>
       <c r="Z32">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA32">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AB32">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
       <c r="AC32">
         <v>1.65</v>
       </c>
       <c r="AD32">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AE32">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF32">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AG32">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>["22"]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5677,30 +5677,30 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P33">
         <v>7.5</v>
       </c>
       <c r="Q33">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R33">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
         <v>1.36</v>
@@ -5727,34 +5727,34 @@
         <v>3.25</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC33">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD33">
         <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AG33">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ33">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6186,22 +6186,22 @@
         <v>4.34</v>
       </c>
       <c r="Q36">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V36">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6210,22 +6210,22 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC36">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
         <v>2.1</v>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -6492,14 +6492,14 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6512,98 +6512,98 @@
         <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA38">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AB38">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
+          <t>["60"]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -7633,118 +7633,118 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O45">
         <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="Q45">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="R45">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T45">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="U45">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="V45">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W45">
+        <v>1.04</v>
+      </c>
+      <c r="X45">
         <v>1.05</v>
       </c>
-      <c r="X45">
+      <c r="Y45">
+        <v>1.36</v>
+      </c>
+      <c r="Z45">
+        <v>2.9</v>
+      </c>
+      <c r="AA45">
+        <v>2.08</v>
+      </c>
+      <c r="AB45">
+        <v>1.66</v>
+      </c>
+      <c r="AC45">
+        <v>4.1</v>
+      </c>
+      <c r="AD45">
+        <v>1.2</v>
+      </c>
+      <c r="AE45">
         <v>1.04</v>
       </c>
-      <c r="Y45">
-        <v>1.33</v>
-      </c>
-      <c r="Z45">
-        <v>3.1</v>
-      </c>
-      <c r="AA45">
-        <v>2.01</v>
-      </c>
-      <c r="AB45">
-        <v>1.7</v>
-      </c>
-      <c r="AC45">
-        <v>3.8</v>
-      </c>
-      <c r="AD45">
-        <v>1.22</v>
-      </c>
-      <c r="AE45">
-        <v>1.05</v>
-      </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
+          <t>["87"]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -7796,42 +7796,42 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="O46">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P46">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="Q46">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="R46">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S46">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="T46">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="U46">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W46">
         <v>1.03</v>
@@ -7840,74 +7840,74 @@
         <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z46">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AA46">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="AB46">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC46">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD46">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG46">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
+          <t>["47", "87"]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK46">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -7959,14 +7959,14 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -7979,98 +7979,98 @@
         <v>5.46</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="R47">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="S47">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T47">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="U47">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="V47">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="Z47">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AB47">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AC47">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD47">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AG47">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
+          <t>["49", "59", "82"]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK47">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL47">
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>2.05</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P48">
         <v>3.25</v>
@@ -8145,19 +8145,19 @@
         <v>2.63</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U48">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
         <v>1.05</v>
@@ -8169,28 +8169,28 @@
         <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA48">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB48">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
         <v>3.25</v>
       </c>
       <c r="AD48">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="O52">
         <v>3</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O53">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P53">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB53">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9280,7 +9280,7 @@
         <v>3.05</v>
       </c>
       <c r="P55">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9446,52 +9446,52 @@
         <v>3.2</v>
       </c>
       <c r="Q56">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="R56">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S56">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T56">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="U56">
-        <v>3.24</v>
+        <v>3.11</v>
       </c>
       <c r="V56">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.36</v>
       </c>
       <c r="Z56">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA56">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB56">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC56">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD56">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG56">
         <v>1.77</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK56">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q57">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="R57">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S57">
+        <v>1.44</v>
+      </c>
+      <c r="T57">
+        <v>2.63</v>
+      </c>
+      <c r="U57">
+        <v>2.86</v>
+      </c>
+      <c r="V57">
+        <v>1.33</v>
+      </c>
+      <c r="W57">
+        <v>1.04</v>
+      </c>
+      <c r="X57">
+        <v>1.04</v>
+      </c>
+      <c r="Y57">
         <v>1.35</v>
       </c>
-      <c r="T57">
-        <v>2.77</v>
-      </c>
-      <c r="U57">
-        <v>2.65</v>
-      </c>
-      <c r="V57">
-        <v>1.38</v>
-      </c>
-      <c r="W57">
-        <v>1.06</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.28</v>
-      </c>
       <c r="Z57">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="AA57">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB57">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC57">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE57">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG57">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
+        <v>2.15</v>
+      </c>
+      <c r="O58">
+        <v>3.3</v>
+      </c>
+      <c r="P58">
+        <v>3.01</v>
+      </c>
+      <c r="Q58">
+        <v>2.75</v>
+      </c>
+      <c r="R58">
         <v>2.1</v>
       </c>
-      <c r="O58">
-        <v>3.2</v>
-      </c>
-      <c r="P58">
-        <v>3.1</v>
-      </c>
-      <c r="Q58">
+      <c r="S58">
+        <v>1.4</v>
+      </c>
+      <c r="T58">
         <v>2.8</v>
       </c>
-      <c r="R58">
-        <v>2.02</v>
-      </c>
-      <c r="S58">
-        <v>1.37</v>
-      </c>
-      <c r="T58">
-        <v>2.69</v>
-      </c>
       <c r="U58">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9802,7 +9802,7 @@
         <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB58">
         <v>1.67</v>
@@ -9817,10 +9817,10 @@
         <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG58">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9903,16 +9903,16 @@
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -9922,47 +9922,47 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
+        <v>2.7</v>
+      </c>
+      <c r="O59">
+        <v>3.1</v>
+      </c>
+      <c r="P59">
+        <v>2.3</v>
+      </c>
+      <c r="Q59">
+        <v>3.19</v>
+      </c>
+      <c r="R59">
+        <v>1.97</v>
+      </c>
+      <c r="S59">
+        <v>1.36</v>
+      </c>
+      <c r="T59">
         <v>2.8</v>
       </c>
-      <c r="O59">
-        <v>3.25</v>
-      </c>
-      <c r="P59">
-        <v>2.4</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA59">
         <v>2.05</v>
@@ -9971,62 +9971,62 @@
         <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "33"]</t>
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10057,139 +10057,139 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="O60">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA60">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB60">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "61", "84"]</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "87"]</t>
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10220,22 +10220,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -10244,115 +10244,115 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N61">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="O61">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="P61">
+        <v>3.6</v>
+      </c>
+      <c r="Q61">
+        <v>2.52</v>
+      </c>
+      <c r="R61">
+        <v>1.91</v>
+      </c>
+      <c r="S61">
+        <v>1.47</v>
+      </c>
+      <c r="T61">
+        <v>2.44</v>
+      </c>
+      <c r="U61">
+        <v>3.1</v>
+      </c>
+      <c r="V61">
+        <v>1.3</v>
+      </c>
+      <c r="W61">
+        <v>1.06</v>
+      </c>
+      <c r="X61">
+        <v>1.05</v>
+      </c>
+      <c r="Y61">
+        <v>1.39</v>
+      </c>
+      <c r="Z61">
+        <v>2.65</v>
+      </c>
+      <c r="AA61">
+        <v>2.35</v>
+      </c>
+      <c r="AB61">
+        <v>1.57</v>
+      </c>
+      <c r="AC61">
+        <v>4.25</v>
+      </c>
+      <c r="AD61">
+        <v>1.15</v>
+      </c>
+      <c r="AE61">
+        <v>1.02</v>
+      </c>
+      <c r="AF61">
+        <v>2.03</v>
+      </c>
+      <c r="AG61">
+        <v>1.69</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>["13"]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>["67"]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.21</v>
+      </c>
+      <c r="AK61">
+        <v>1.55</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>2</v>
+      </c>
+      <c r="AN61">
         <v>3</v>
       </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>0</v>
-      </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>2.2</v>
-      </c>
-      <c r="AB61">
-        <v>1.65</v>
-      </c>
-      <c r="AC61">
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
-      <c r="AE61">
-        <v>0</v>
-      </c>
-      <c r="AF61">
-        <v>0</v>
-      </c>
-      <c r="AG61">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>0</v>
-      </c>
-      <c r="AK61">
-        <v>0</v>
-      </c>
-      <c r="AL61">
-        <v>0</v>
-      </c>
-      <c r="AM61">
-        <v>-1</v>
-      </c>
-      <c r="AN61">
-        <v>-1</v>
-      </c>
       <c r="AO61">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP61">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
@@ -10383,112 +10383,112 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
         <v>3.2</v>
       </c>
       <c r="P62">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AA62">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB62">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "63"]</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "39", "64", "68", "70"]</t>
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,25 +10587,25 @@
         <v>2.39</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R63">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S63">
         <v>1.4</v>
       </c>
       <c r="T63">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="U63">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10617,16 +10617,16 @@
         <v>2.88</v>
       </c>
       <c r="AA63">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB63">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC63">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="AD63">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE63">
         <v>1.02</v>
@@ -10651,7 +10651,7 @@
         <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10759,7 +10759,7 @@
         <v>1.36</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U64">
         <v>2.8</v>
@@ -10768,7 +10768,7 @@
         <v>1.36</v>
       </c>
       <c r="W64">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
         <v>1</v>
@@ -10904,22 +10904,22 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q65">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T65">
         <v>2.58</v>
@@ -10937,31 +10937,31 @@
         <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z65">
         <v>2.74</v>
       </c>
       <c r="AA65">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB65">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC65">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AD65">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE65">
         <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK65">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q66">
         <v>2.3</v>
@@ -11109,10 +11109,10 @@
         <v>2.15</v>
       </c>
       <c r="AB66">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC66">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD66">
         <v>1.19</v>
@@ -11121,10 +11121,10 @@
         <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG66">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11361,19 +11361,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -11385,72 +11385,72 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N68">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="O68">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="Q68">
-        <v>3.43</v>
+        <v>2.93</v>
       </c>
       <c r="R68">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S68">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U68">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z68">
-        <v>2.83</v>
+        <v>3.36</v>
       </c>
       <c r="AA68">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AB68">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC68">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD68">
         <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG68">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11459,41 +11459,41 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ68">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL68">
         <v>0</v>
       </c>
       <c r="AM68">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN68">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO68">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP68">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS68">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
@@ -11524,96 +11524,96 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69">
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N69">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q69">
+        <v>3.48</v>
+      </c>
+      <c r="R69">
+        <v>2.1</v>
+      </c>
+      <c r="S69">
+        <v>1.42</v>
+      </c>
+      <c r="T69">
+        <v>2.51</v>
+      </c>
+      <c r="U69">
         <v>2.88</v>
       </c>
-      <c r="R69">
-        <v>2.11</v>
-      </c>
-      <c r="S69">
-        <v>1.37</v>
-      </c>
-      <c r="T69">
-        <v>2.75</v>
-      </c>
-      <c r="U69">
-        <v>3.2</v>
-      </c>
       <c r="V69">
+        <v>1.36</v>
+      </c>
+      <c r="W69">
+        <v>1.06</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
         <v>1.33</v>
       </c>
-      <c r="W69">
-        <v>1.07</v>
-      </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.3</v>
-      </c>
       <c r="Z69">
-        <v>3.31</v>
+        <v>2.83</v>
       </c>
       <c r="AA69">
         <v>2.15</v>
       </c>
       <c r="AB69">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC69">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD69">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE69">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF69">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG69">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11622,41 +11622,41 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "44", "90+2"]</t>
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AL69">
         <v>0</v>
       </c>
       <c r="AM69">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN69">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO69">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP69">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ69">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS69">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT69">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB70">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O72">
         <v>3.2</v>
       </c>
       <c r="P72">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB72">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O73">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P73">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q73">
-        <v>3.77</v>
+        <v>3.2</v>
       </c>
       <c r="R73">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S73">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T73">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="U73">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y73">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="Z73">
-        <v>3.14</v>
+        <v>2.52</v>
       </c>
       <c r="AA73">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AB73">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC73">
-        <v>3.34</v>
+        <v>4.65</v>
       </c>
       <c r="AD73">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE73">
         <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AG73">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK73">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.87</v>
+        <v>2.46</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12674,10 +12674,10 @@
         </is>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -12686,118 +12686,118 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL76">
         <v>0</v>
       </c>
       <c r="AM76">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN76">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO76">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP76">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS76">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT76">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         </is>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -12849,118 +12849,118 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N77">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P77">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA77">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB77">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
+          <t>["83"]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL77">
         <v>0</v>
       </c>
       <c r="AM77">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN77">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO77">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP77">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ77">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR77">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS77">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT77">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -13012,118 +13012,118 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O78">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA78">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AB78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
+          <t>["74", "82"]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
       </c>
       <c r="AM78">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN78">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO78">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP78">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR78">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS78">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT78">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>3.3</v>
       </c>
       <c r="P79">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13521,16 +13521,16 @@
         <v>3.8</v>
       </c>
       <c r="Q81">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R81">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T81">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="U81">
         <v>2.82</v>
@@ -13545,16 +13545,16 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z81">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA81">
         <v>2.1</v>
       </c>
       <c r="AB81">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC81">
         <v>3.42</v>
@@ -13566,10 +13566,10 @@
         <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG81">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.31</v>
       </c>
       <c r="AK81">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O82">
         <v>3.35</v>
@@ -13690,19 +13690,19 @@
         <v>2.15</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T82">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="U82">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V82">
         <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13714,13 +13714,13 @@
         <v>3.5</v>
       </c>
       <c r="AA82">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AB82">
         <v>1.9</v>
       </c>
       <c r="AC82">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="AD82">
         <v>1.31</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK82">
         <v>1.75</v>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -13827,118 +13827,118 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N83">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P83">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q83">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="U83">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V83">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
         <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z83">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA83">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB83">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC83">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AD83">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE83">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG83">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
+          <t>["67"]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AL83">
         <v>0</v>
       </c>
       <c r="AM83">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN83">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO83">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP83">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ83">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS83">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT83">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O84">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB84">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="O85">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="P85">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB85">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB86">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -14479,118 +14479,118 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N87">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="O87">
+        <v>2.8</v>
+      </c>
+      <c r="P87">
         <v>3.25</v>
       </c>
-      <c r="P87">
-        <v>2.88</v>
-      </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA87">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB87">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
+          <t>["52"]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL87">
         <v>0</v>
       </c>
       <c r="AM87">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN87">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP87">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ87">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR87">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS87">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT87">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="N90">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P90">
         <v>2.2</v>
@@ -14997,7 +14997,7 @@
         <v>1.26</v>
       </c>
       <c r="T90">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U90">
         <v>2.4</v>
@@ -15009,13 +15009,13 @@
         <v>1.09</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
         <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA90">
         <v>1.71</v>
@@ -15027,10 +15027,10 @@
         <v>2.76</v>
       </c>
       <c r="AD90">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE90">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF90">
         <v>1.56</v>
@@ -15052,7 +15052,7 @@
         <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O95">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P95">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="O96">
+        <v>3.15</v>
+      </c>
+      <c r="P96">
         <v>3.1</v>
-      </c>
-      <c r="P96">
-        <v>3.33</v>
       </c>
       <c r="Q96">
         <v>2.88</v>
@@ -15981,7 +15981,7 @@
         <v>3</v>
       </c>
       <c r="V96">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W96">
         <v>1.06</v>
@@ -16097,10 +16097,10 @@
         </is>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -16109,42 +16109,42 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N97">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="O97">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P97">
-        <v>3.49</v>
+        <v>3.35</v>
       </c>
       <c r="Q97">
         <v>2.62</v>
       </c>
       <c r="R97">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S97">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T97">
         <v>2.48</v>
       </c>
       <c r="U97">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V97">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W97">
         <v>1.01</v>
@@ -16159,13 +16159,13 @@
         <v>2.74</v>
       </c>
       <c r="AA97">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB97">
         <v>1.61</v>
       </c>
       <c r="AC97">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD97">
         <v>1.16</v>
@@ -16174,53 +16174,53 @@
         <v>1.01</v>
       </c>
       <c r="AF97">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG97">
         <v>1.75</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ97">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK97">
+        <v>1.57</v>
+      </c>
+      <c r="AL97">
+        <v>0</v>
+      </c>
+      <c r="AM97">
+        <v>4</v>
+      </c>
+      <c r="AN97">
+        <v>1</v>
+      </c>
+      <c r="AO97">
+        <v>15</v>
+      </c>
+      <c r="AP97">
+        <v>15</v>
+      </c>
+      <c r="AQ97">
+        <v>1.8</v>
+      </c>
+      <c r="AR97">
         <v>1.61</v>
       </c>
-      <c r="AL97">
-        <v>0</v>
-      </c>
-      <c r="AM97">
-        <v>-1</v>
-      </c>
-      <c r="AN97">
-        <v>-1</v>
-      </c>
-      <c r="AO97">
-        <v>-1</v>
-      </c>
-      <c r="AP97">
-        <v>-1</v>
-      </c>
-      <c r="AQ97">
-        <v>0</v>
-      </c>
-      <c r="AR97">
-        <v>0</v>
-      </c>
       <c r="AS97">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT97">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
@@ -16609,31 +16609,31 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="O100">
         <v>3.1</v>
       </c>
       <c r="P100">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="Q100">
         <v>2.6</v>
       </c>
       <c r="R100">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S100">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T100">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U100">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V100">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W100">
         <v>1.03</v>
@@ -16642,31 +16642,31 @@
         <v>1.1</v>
       </c>
       <c r="Y100">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z100">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AA100">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AB100">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AC100">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AD100">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE100">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF100">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG100">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>1.35</v>
       </c>
       <c r="AK100">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,22 +16772,22 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="O101">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q101">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R101">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="S101">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T101">
         <v>2.5</v>
@@ -16802,34 +16802,34 @@
         <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z101">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AA101">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AB101">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC101">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="AD101">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE101">
         <v>1.03</v>
       </c>
       <c r="AF101">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG101">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O114">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P114">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q114">
         <v>2.27</v>
       </c>
       <c r="R114">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="S114">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T114">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="U114">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V114">
+        <v>1.33</v>
+      </c>
+      <c r="W114">
+        <v>1.02</v>
+      </c>
+      <c r="X114">
+        <v>1.03</v>
+      </c>
+      <c r="Y114">
         <v>1.29</v>
       </c>
-      <c r="W114">
-        <v>1.01</v>
-      </c>
-      <c r="X114">
-        <v>1.02</v>
-      </c>
-      <c r="Y114">
-        <v>1.35</v>
-      </c>
       <c r="Z114">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AA114">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="AB114">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC114">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD114">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE114">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF114">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AG114">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK114">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P115">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="O117">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="P117">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X117">
         <v>0</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC117">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD117">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL119">
         <v>0</v>
